--- a/backend/data/mlb/Combined_Daily_Data.xlsx
+++ b/backend/data/mlb/Combined_Daily_Data.xlsx
@@ -655,7 +655,7 @@
     <t>LHP</t>
   </si>
   <si>
-    <t>May 11</t>
+    <t>May 12</t>
   </si>
 </sst>
 </file>
@@ -2655,46 +2655,46 @@
         <v>197</v>
       </c>
       <c r="AD11">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AE11">
         <v>10</v>
       </c>
       <c r="AF11">
-        <v>0.245</v>
+        <v>0.232</v>
       </c>
       <c r="AG11">
-        <v>0.3172076923076923</v>
+        <v>0.3053928571428571</v>
       </c>
       <c r="AH11">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AI11">
-        <v>0.1771076923076923</v>
+        <v>0.1651642857142858</v>
       </c>
       <c r="AJ11">
-        <v>0.4217153846153846</v>
+        <v>0.3975214285714286</v>
       </c>
       <c r="AK11">
-        <v>22.666</v>
+        <v>24.259</v>
       </c>
       <c r="AL11">
-        <v>7.306153846153846</v>
+        <v>7.865</v>
       </c>
       <c r="AM11">
-        <v>4.281384615384615</v>
+        <v>4.062142857142858</v>
       </c>
       <c r="AN11">
-        <v>42.46692307692307</v>
+        <v>43.88642857142857</v>
       </c>
       <c r="AO11">
-        <v>39.16846153846154</v>
+        <v>38.58142857142857</v>
       </c>
       <c r="AP11">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="AQ11">
-        <v>30.93076923076923</v>
+        <v>30.64857142857143</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -2810,46 +2810,46 @@
         <v>197</v>
       </c>
       <c r="AD12">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AE12">
         <v>10</v>
       </c>
       <c r="AF12">
-        <v>0.245</v>
+        <v>0.232</v>
       </c>
       <c r="AG12">
-        <v>0.3172076923076923</v>
+        <v>0.3053928571428571</v>
       </c>
       <c r="AH12">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AI12">
-        <v>0.1771076923076923</v>
+        <v>0.1651642857142858</v>
       </c>
       <c r="AJ12">
-        <v>0.4217153846153846</v>
+        <v>0.3975214285714286</v>
       </c>
       <c r="AK12">
-        <v>22.666</v>
+        <v>24.259</v>
       </c>
       <c r="AL12">
-        <v>7.306153846153846</v>
+        <v>7.865</v>
       </c>
       <c r="AM12">
-        <v>4.281384615384615</v>
+        <v>4.062142857142858</v>
       </c>
       <c r="AN12">
-        <v>42.46692307692307</v>
+        <v>43.88642857142857</v>
       </c>
       <c r="AO12">
-        <v>39.16846153846154</v>
+        <v>38.58142857142857</v>
       </c>
       <c r="AP12">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="AQ12">
-        <v>30.93076923076923</v>
+        <v>30.64857142857143</v>
       </c>
       <c r="AR12">
         <v>1</v>
@@ -2965,46 +2965,46 @@
         <v>197</v>
       </c>
       <c r="AD13">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AE13">
         <v>10</v>
       </c>
       <c r="AF13">
-        <v>0.245</v>
+        <v>0.232</v>
       </c>
       <c r="AG13">
-        <v>0.3172076923076923</v>
+        <v>0.3053928571428571</v>
       </c>
       <c r="AH13">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AI13">
-        <v>0.1771076923076923</v>
+        <v>0.1651642857142858</v>
       </c>
       <c r="AJ13">
-        <v>0.4217153846153846</v>
+        <v>0.3975214285714286</v>
       </c>
       <c r="AK13">
-        <v>22.666</v>
+        <v>24.259</v>
       </c>
       <c r="AL13">
-        <v>7.306153846153846</v>
+        <v>7.865</v>
       </c>
       <c r="AM13">
-        <v>4.281384615384615</v>
+        <v>4.062142857142858</v>
       </c>
       <c r="AN13">
-        <v>42.46692307692307</v>
+        <v>43.88642857142857</v>
       </c>
       <c r="AO13">
-        <v>39.16846153846154</v>
+        <v>38.58142857142857</v>
       </c>
       <c r="AP13">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="AQ13">
-        <v>30.93076923076923</v>
+        <v>30.64857142857143</v>
       </c>
       <c r="AR13">
         <v>1</v>
@@ -3120,46 +3120,46 @@
         <v>198</v>
       </c>
       <c r="AD14">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AE14">
         <v>3</v>
       </c>
       <c r="AF14">
-        <v>0.246</v>
+        <v>0.234</v>
       </c>
       <c r="AG14">
-        <v>0.3015</v>
+        <v>0.2880895522388059</v>
       </c>
       <c r="AH14">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AI14">
-        <v>0.167</v>
+        <v>0.1595223880597015</v>
       </c>
       <c r="AJ14">
-        <v>0.4125</v>
+        <v>0.3935671641791044</v>
       </c>
       <c r="AK14">
-        <v>35.95</v>
+        <v>34.351</v>
       </c>
       <c r="AL14">
-        <v>4.7</v>
+        <v>4.523880597014925</v>
       </c>
       <c r="AM14">
-        <v>3.34</v>
+        <v>3.386268656716418</v>
       </c>
       <c r="AN14">
-        <v>41.5</v>
+        <v>43.72388059701493</v>
       </c>
       <c r="AO14">
-        <v>31.25</v>
+        <v>32.13432835820895</v>
       </c>
       <c r="AP14">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="AQ14">
-        <v>26.15</v>
+        <v>24.06119402985075</v>
       </c>
       <c r="AR14">
         <v>1</v>
@@ -3275,46 +3275,46 @@
         <v>197</v>
       </c>
       <c r="AD15">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AE15">
         <v>10</v>
       </c>
       <c r="AF15">
-        <v>0.245</v>
+        <v>0.232</v>
       </c>
       <c r="AG15">
-        <v>0.3172076923076923</v>
+        <v>0.3053928571428571</v>
       </c>
       <c r="AH15">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AI15">
-        <v>0.1771076923076923</v>
+        <v>0.1651642857142858</v>
       </c>
       <c r="AJ15">
-        <v>0.4217153846153846</v>
+        <v>0.3975214285714286</v>
       </c>
       <c r="AK15">
-        <v>22.666</v>
+        <v>24.259</v>
       </c>
       <c r="AL15">
-        <v>7.306153846153846</v>
+        <v>7.865</v>
       </c>
       <c r="AM15">
-        <v>4.281384615384615</v>
+        <v>4.062142857142858</v>
       </c>
       <c r="AN15">
-        <v>42.46692307692307</v>
+        <v>43.88642857142857</v>
       </c>
       <c r="AO15">
-        <v>39.16846153846154</v>
+        <v>38.58142857142857</v>
       </c>
       <c r="AP15">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="AQ15">
-        <v>30.93076923076923</v>
+        <v>30.64857142857143</v>
       </c>
       <c r="AR15">
         <v>1</v>
@@ -3430,46 +3430,46 @@
         <v>197</v>
       </c>
       <c r="AD16">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AE16">
         <v>10</v>
       </c>
       <c r="AF16">
-        <v>0.245</v>
+        <v>0.232</v>
       </c>
       <c r="AG16">
-        <v>0.3172076923076923</v>
+        <v>0.3053928571428571</v>
       </c>
       <c r="AH16">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AI16">
-        <v>0.1771076923076923</v>
+        <v>0.1651642857142858</v>
       </c>
       <c r="AJ16">
-        <v>0.4217153846153846</v>
+        <v>0.3975214285714286</v>
       </c>
       <c r="AK16">
-        <v>22.666</v>
+        <v>24.259</v>
       </c>
       <c r="AL16">
-        <v>7.306153846153846</v>
+        <v>7.865</v>
       </c>
       <c r="AM16">
-        <v>4.281384615384615</v>
+        <v>4.062142857142858</v>
       </c>
       <c r="AN16">
-        <v>42.46692307692307</v>
+        <v>43.88642857142857</v>
       </c>
       <c r="AO16">
-        <v>39.16846153846154</v>
+        <v>38.58142857142857</v>
       </c>
       <c r="AP16">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="AQ16">
-        <v>30.93076923076923</v>
+        <v>30.64857142857143</v>
       </c>
       <c r="AR16">
         <v>1</v>
@@ -3585,46 +3585,46 @@
         <v>197</v>
       </c>
       <c r="AD17">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AE17">
         <v>10</v>
       </c>
       <c r="AF17">
-        <v>0.245</v>
+        <v>0.232</v>
       </c>
       <c r="AG17">
-        <v>0.3172076923076923</v>
+        <v>0.3053928571428571</v>
       </c>
       <c r="AH17">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AI17">
-        <v>0.1771076923076923</v>
+        <v>0.1651642857142858</v>
       </c>
       <c r="AJ17">
-        <v>0.4217153846153846</v>
+        <v>0.3975214285714286</v>
       </c>
       <c r="AK17">
-        <v>22.666</v>
+        <v>24.259</v>
       </c>
       <c r="AL17">
-        <v>7.306153846153846</v>
+        <v>7.865</v>
       </c>
       <c r="AM17">
-        <v>4.281384615384615</v>
+        <v>4.062142857142858</v>
       </c>
       <c r="AN17">
-        <v>42.46692307692307</v>
+        <v>43.88642857142857</v>
       </c>
       <c r="AO17">
-        <v>39.16846153846154</v>
+        <v>38.58142857142857</v>
       </c>
       <c r="AP17">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="AQ17">
-        <v>30.93076923076923</v>
+        <v>30.64857142857143</v>
       </c>
       <c r="AR17">
         <v>1</v>
@@ -3740,46 +3740,46 @@
         <v>197</v>
       </c>
       <c r="AD18">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AE18">
         <v>10</v>
       </c>
       <c r="AF18">
-        <v>0.245</v>
+        <v>0.232</v>
       </c>
       <c r="AG18">
-        <v>0.3172076923076923</v>
+        <v>0.3053928571428571</v>
       </c>
       <c r="AH18">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AI18">
-        <v>0.1771076923076923</v>
+        <v>0.1651642857142858</v>
       </c>
       <c r="AJ18">
-        <v>0.4217153846153846</v>
+        <v>0.3975214285714286</v>
       </c>
       <c r="AK18">
-        <v>22.666</v>
+        <v>24.259</v>
       </c>
       <c r="AL18">
-        <v>7.306153846153846</v>
+        <v>7.865</v>
       </c>
       <c r="AM18">
-        <v>4.281384615384615</v>
+        <v>4.062142857142858</v>
       </c>
       <c r="AN18">
-        <v>42.46692307692307</v>
+        <v>43.88642857142857</v>
       </c>
       <c r="AO18">
-        <v>39.16846153846154</v>
+        <v>38.58142857142857</v>
       </c>
       <c r="AP18">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="AQ18">
-        <v>30.93076923076923</v>
+        <v>30.64857142857143</v>
       </c>
       <c r="AR18">
         <v>1</v>
@@ -3895,46 +3895,46 @@
         <v>197</v>
       </c>
       <c r="AD19">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AE19">
         <v>10</v>
       </c>
       <c r="AF19">
-        <v>0.245</v>
+        <v>0.232</v>
       </c>
       <c r="AG19">
-        <v>0.3172076923076923</v>
+        <v>0.3053928571428571</v>
       </c>
       <c r="AH19">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AI19">
-        <v>0.1771076923076923</v>
+        <v>0.1651642857142858</v>
       </c>
       <c r="AJ19">
-        <v>0.4217153846153846</v>
+        <v>0.3975214285714286</v>
       </c>
       <c r="AK19">
-        <v>22.666</v>
+        <v>24.259</v>
       </c>
       <c r="AL19">
-        <v>7.306153846153846</v>
+        <v>7.865</v>
       </c>
       <c r="AM19">
-        <v>4.281384615384615</v>
+        <v>4.062142857142858</v>
       </c>
       <c r="AN19">
-        <v>42.46692307692307</v>
+        <v>43.88642857142857</v>
       </c>
       <c r="AO19">
-        <v>39.16846153846154</v>
+        <v>38.58142857142857</v>
       </c>
       <c r="AP19">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="AQ19">
-        <v>30.93076923076923</v>
+        <v>30.64857142857143</v>
       </c>
       <c r="AR19">
         <v>1</v>
@@ -4050,46 +4050,46 @@
         <v>198</v>
       </c>
       <c r="AD20">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="AM20">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="AO20">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="AP20">
         <v>0</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="AR20">
         <v>1</v>
@@ -4205,46 +4205,46 @@
         <v>198</v>
       </c>
       <c r="AD21">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="AM21">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="AO21">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="AP21">
         <v>0</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -4360,46 +4360,46 @@
         <v>198</v>
       </c>
       <c r="AD22">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="AM22">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="AO22">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="AP22">
         <v>0</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -4515,46 +4515,46 @@
         <v>198</v>
       </c>
       <c r="AD23">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="AM23">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="AO23">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="AP23">
         <v>0</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="AR23">
         <v>1</v>
@@ -4670,46 +4670,46 @@
         <v>198</v>
       </c>
       <c r="AD24">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="AM24">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="AO24">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="AP24">
         <v>0</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -4825,46 +4825,46 @@
         <v>198</v>
       </c>
       <c r="AD25">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="AM25">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="AO25">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="AP25">
         <v>0</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="AR25">
         <v>1</v>
@@ -4980,46 +4980,46 @@
         <v>198</v>
       </c>
       <c r="AD26">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="AM26">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="AO26">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="AP26">
         <v>0</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="AR26">
         <v>1</v>
@@ -5135,46 +5135,46 @@
         <v>198</v>
       </c>
       <c r="AD27">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="AM27">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="AO27">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="AP27">
         <v>0</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -5290,46 +5290,46 @@
         <v>198</v>
       </c>
       <c r="AD28">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="AM28">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="AO28">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="AP28">
         <v>0</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -5445,46 +5445,46 @@
         <v>198</v>
       </c>
       <c r="AD29">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AE29">
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>0.247</v>
+        <v>0.244</v>
       </c>
       <c r="AG29">
-        <v>0.302420253164557</v>
+        <v>0.2986253101736973</v>
       </c>
       <c r="AH29">
         <v>2.5</v>
       </c>
       <c r="AI29">
-        <v>0.122832911392405</v>
+        <v>0.1201290322580645</v>
       </c>
       <c r="AJ29">
-        <v>0.3694101265822785</v>
+        <v>0.3640496277915632</v>
       </c>
       <c r="AK29">
-        <v>23.536</v>
+        <v>23.81</v>
       </c>
       <c r="AL29">
-        <v>7.814936708860759</v>
+        <v>7.649627791563275</v>
       </c>
       <c r="AM29">
-        <v>3.652886075949367</v>
+        <v>3.583498759305211</v>
       </c>
       <c r="AN29">
-        <v>49.8820253164557</v>
+        <v>50.05285359801489</v>
       </c>
       <c r="AO29">
-        <v>32.33063291139241</v>
+        <v>32.10198511166253</v>
       </c>
       <c r="AP29">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="AQ29">
-        <v>33.0486075949367</v>
+        <v>33.53498759305211</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -5600,46 +5600,46 @@
         <v>197</v>
       </c>
       <c r="AD30">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="AE30">
         <v>9</v>
       </c>
       <c r="AF30">
-        <v>0.249</v>
+        <v>0.257</v>
       </c>
       <c r="AG30">
-        <v>0.2852612612612613</v>
+        <v>0.2925862068965518</v>
       </c>
       <c r="AH30">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AI30">
-        <v>0.1274864864864865</v>
+        <v>0.122551724137931</v>
       </c>
       <c r="AJ30">
-        <v>0.3765405405405405</v>
+        <v>0.3798620689655172</v>
       </c>
       <c r="AK30">
-        <v>24.941</v>
+        <v>25.024</v>
       </c>
       <c r="AL30">
-        <v>3.045945945945946</v>
+        <v>3.489655172413793</v>
       </c>
       <c r="AM30">
-        <v>3.078468468468468</v>
+        <v>3.061724137931035</v>
       </c>
       <c r="AN30">
-        <v>45.61531531531531</v>
+        <v>45.69655172413793</v>
       </c>
       <c r="AO30">
-        <v>33.95675675675675</v>
+        <v>32.72758620689655</v>
       </c>
       <c r="AP30">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ30">
-        <v>30.7963963963964</v>
+        <v>31.22758620689655</v>
       </c>
       <c r="AR30">
         <v>1</v>
@@ -5755,46 +5755,46 @@
         <v>197</v>
       </c>
       <c r="AD31">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="AE31">
         <v>9</v>
       </c>
       <c r="AF31">
-        <v>0.249</v>
+        <v>0.257</v>
       </c>
       <c r="AG31">
-        <v>0.2852612612612613</v>
+        <v>0.2925862068965518</v>
       </c>
       <c r="AH31">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AI31">
-        <v>0.1274864864864865</v>
+        <v>0.122551724137931</v>
       </c>
       <c r="AJ31">
-        <v>0.3765405405405405</v>
+        <v>0.3798620689655172</v>
       </c>
       <c r="AK31">
-        <v>24.941</v>
+        <v>25.024</v>
       </c>
       <c r="AL31">
-        <v>3.045945945945946</v>
+        <v>3.489655172413793</v>
       </c>
       <c r="AM31">
-        <v>3.078468468468468</v>
+        <v>3.061724137931035</v>
       </c>
       <c r="AN31">
-        <v>45.61531531531531</v>
+        <v>45.69655172413793</v>
       </c>
       <c r="AO31">
-        <v>33.95675675675675</v>
+        <v>32.72758620689655</v>
       </c>
       <c r="AP31">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ31">
-        <v>30.7963963963964</v>
+        <v>31.22758620689655</v>
       </c>
       <c r="AR31">
         <v>1</v>
@@ -5910,46 +5910,46 @@
         <v>197</v>
       </c>
       <c r="AD32">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="AE32">
         <v>9</v>
       </c>
       <c r="AF32">
-        <v>0.249</v>
+        <v>0.257</v>
       </c>
       <c r="AG32">
-        <v>0.2852612612612613</v>
+        <v>0.2925862068965518</v>
       </c>
       <c r="AH32">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AI32">
-        <v>0.1274864864864865</v>
+        <v>0.122551724137931</v>
       </c>
       <c r="AJ32">
-        <v>0.3765405405405405</v>
+        <v>0.3798620689655172</v>
       </c>
       <c r="AK32">
-        <v>24.941</v>
+        <v>25.024</v>
       </c>
       <c r="AL32">
-        <v>3.045945945945946</v>
+        <v>3.489655172413793</v>
       </c>
       <c r="AM32">
-        <v>3.078468468468468</v>
+        <v>3.061724137931035</v>
       </c>
       <c r="AN32">
-        <v>45.61531531531531</v>
+        <v>45.69655172413793</v>
       </c>
       <c r="AO32">
-        <v>33.95675675675675</v>
+        <v>32.72758620689655</v>
       </c>
       <c r="AP32">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ32">
-        <v>30.7963963963964</v>
+        <v>31.22758620689655</v>
       </c>
       <c r="AR32">
         <v>0</v>
@@ -6065,46 +6065,46 @@
         <v>197</v>
       </c>
       <c r="AD33">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="AE33">
         <v>9</v>
       </c>
       <c r="AF33">
-        <v>0.249</v>
+        <v>0.257</v>
       </c>
       <c r="AG33">
-        <v>0.2852612612612613</v>
+        <v>0.2925862068965518</v>
       </c>
       <c r="AH33">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AI33">
-        <v>0.1274864864864865</v>
+        <v>0.122551724137931</v>
       </c>
       <c r="AJ33">
-        <v>0.3765405405405405</v>
+        <v>0.3798620689655172</v>
       </c>
       <c r="AK33">
-        <v>24.941</v>
+        <v>25.024</v>
       </c>
       <c r="AL33">
-        <v>3.045945945945946</v>
+        <v>3.489655172413793</v>
       </c>
       <c r="AM33">
-        <v>3.078468468468468</v>
+        <v>3.061724137931035</v>
       </c>
       <c r="AN33">
-        <v>45.61531531531531</v>
+        <v>45.69655172413793</v>
       </c>
       <c r="AO33">
-        <v>33.95675675675675</v>
+        <v>32.72758620689655</v>
       </c>
       <c r="AP33">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ33">
-        <v>30.7963963963964</v>
+        <v>31.22758620689655</v>
       </c>
       <c r="AR33">
         <v>1</v>
@@ -6220,46 +6220,46 @@
         <v>197</v>
       </c>
       <c r="AD34">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="AE34">
         <v>9</v>
       </c>
       <c r="AF34">
-        <v>0.249</v>
+        <v>0.257</v>
       </c>
       <c r="AG34">
-        <v>0.2852612612612613</v>
+        <v>0.2925862068965518</v>
       </c>
       <c r="AH34">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AI34">
-        <v>0.1274864864864865</v>
+        <v>0.122551724137931</v>
       </c>
       <c r="AJ34">
-        <v>0.3765405405405405</v>
+        <v>0.3798620689655172</v>
       </c>
       <c r="AK34">
-        <v>24.941</v>
+        <v>25.024</v>
       </c>
       <c r="AL34">
-        <v>3.045945945945946</v>
+        <v>3.489655172413793</v>
       </c>
       <c r="AM34">
-        <v>3.078468468468468</v>
+        <v>3.061724137931035</v>
       </c>
       <c r="AN34">
-        <v>45.61531531531531</v>
+        <v>45.69655172413793</v>
       </c>
       <c r="AO34">
-        <v>33.95675675675675</v>
+        <v>32.72758620689655</v>
       </c>
       <c r="AP34">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ34">
-        <v>30.7963963963964</v>
+        <v>31.22758620689655</v>
       </c>
       <c r="AR34">
         <v>0</v>
@@ -6375,46 +6375,46 @@
         <v>197</v>
       </c>
       <c r="AD35">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="AE35">
         <v>9</v>
       </c>
       <c r="AF35">
-        <v>0.249</v>
+        <v>0.257</v>
       </c>
       <c r="AG35">
-        <v>0.2852612612612613</v>
+        <v>0.2925862068965518</v>
       </c>
       <c r="AH35">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AI35">
-        <v>0.1274864864864865</v>
+        <v>0.122551724137931</v>
       </c>
       <c r="AJ35">
-        <v>0.3765405405405405</v>
+        <v>0.3798620689655172</v>
       </c>
       <c r="AK35">
-        <v>24.941</v>
+        <v>25.024</v>
       </c>
       <c r="AL35">
-        <v>3.045945945945946</v>
+        <v>3.489655172413793</v>
       </c>
       <c r="AM35">
-        <v>3.078468468468468</v>
+        <v>3.061724137931035</v>
       </c>
       <c r="AN35">
-        <v>45.61531531531531</v>
+        <v>45.69655172413793</v>
       </c>
       <c r="AO35">
-        <v>33.95675675675675</v>
+        <v>32.72758620689655</v>
       </c>
       <c r="AP35">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ35">
-        <v>30.7963963963964</v>
+        <v>31.22758620689655</v>
       </c>
       <c r="AR35">
         <v>0</v>
@@ -6530,46 +6530,46 @@
         <v>198</v>
       </c>
       <c r="AD36">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AE36">
         <v>10</v>
       </c>
       <c r="AF36">
-        <v>0.247</v>
+        <v>0.244</v>
       </c>
       <c r="AG36">
-        <v>0.302420253164557</v>
+        <v>0.2986253101736973</v>
       </c>
       <c r="AH36">
         <v>2.5</v>
       </c>
       <c r="AI36">
-        <v>0.122832911392405</v>
+        <v>0.1201290322580645</v>
       </c>
       <c r="AJ36">
-        <v>0.3694101265822785</v>
+        <v>0.3640496277915632</v>
       </c>
       <c r="AK36">
-        <v>23.536</v>
+        <v>23.81</v>
       </c>
       <c r="AL36">
-        <v>7.814936708860759</v>
+        <v>7.649627791563275</v>
       </c>
       <c r="AM36">
-        <v>3.652886075949367</v>
+        <v>3.583498759305211</v>
       </c>
       <c r="AN36">
-        <v>49.8820253164557</v>
+        <v>50.05285359801489</v>
       </c>
       <c r="AO36">
-        <v>32.33063291139241</v>
+        <v>32.10198511166253</v>
       </c>
       <c r="AP36">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="AQ36">
-        <v>33.0486075949367</v>
+        <v>33.53498759305211</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -6685,46 +6685,46 @@
         <v>198</v>
       </c>
       <c r="AD37">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AE37">
         <v>10</v>
       </c>
       <c r="AF37">
-        <v>0.247</v>
+        <v>0.244</v>
       </c>
       <c r="AG37">
-        <v>0.302420253164557</v>
+        <v>0.2986253101736973</v>
       </c>
       <c r="AH37">
         <v>2.5</v>
       </c>
       <c r="AI37">
-        <v>0.122832911392405</v>
+        <v>0.1201290322580645</v>
       </c>
       <c r="AJ37">
-        <v>0.3694101265822785</v>
+        <v>0.3640496277915632</v>
       </c>
       <c r="AK37">
-        <v>23.536</v>
+        <v>23.81</v>
       </c>
       <c r="AL37">
-        <v>7.814936708860759</v>
+        <v>7.649627791563275</v>
       </c>
       <c r="AM37">
-        <v>3.652886075949367</v>
+        <v>3.583498759305211</v>
       </c>
       <c r="AN37">
-        <v>49.8820253164557</v>
+        <v>50.05285359801489</v>
       </c>
       <c r="AO37">
-        <v>32.33063291139241</v>
+        <v>32.10198511166253</v>
       </c>
       <c r="AP37">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="AQ37">
-        <v>33.0486075949367</v>
+        <v>33.53498759305211</v>
       </c>
       <c r="AR37">
         <v>1</v>
@@ -6840,46 +6840,46 @@
         <v>197</v>
       </c>
       <c r="AD38">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="AE38">
         <v>11</v>
       </c>
       <c r="AF38">
-        <v>0.224</v>
+        <v>0.219</v>
       </c>
       <c r="AG38">
-        <v>0.3002912621359223</v>
+        <v>0.2944364896073903</v>
       </c>
       <c r="AH38">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AI38">
-        <v>0.1485339805825243</v>
+        <v>0.1430230946882218</v>
       </c>
       <c r="AJ38">
-        <v>0.3720970873786408</v>
+        <v>0.3624272517321017</v>
       </c>
       <c r="AK38">
-        <v>26.685</v>
+        <v>26.325</v>
       </c>
       <c r="AL38">
-        <v>10.41456310679612</v>
+        <v>10.13856812933025</v>
       </c>
       <c r="AM38">
-        <v>3.71757281553398</v>
+        <v>3.625150115473441</v>
       </c>
       <c r="AN38">
-        <v>42.18349514563107</v>
+        <v>42.64041570438799</v>
       </c>
       <c r="AO38">
-        <v>38.6747572815534</v>
+        <v>38.5729792147806</v>
       </c>
       <c r="AP38">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="AQ38">
-        <v>34.12135922330097</v>
+        <v>32.49445727482679</v>
       </c>
       <c r="AR38">
         <v>1</v>
@@ -6995,46 +6995,46 @@
         <v>197</v>
       </c>
       <c r="AD39">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="AE39">
         <v>11</v>
       </c>
       <c r="AF39">
-        <v>0.224</v>
+        <v>0.219</v>
       </c>
       <c r="AG39">
-        <v>0.3002912621359223</v>
+        <v>0.2944364896073903</v>
       </c>
       <c r="AH39">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AI39">
-        <v>0.1485339805825243</v>
+        <v>0.1430230946882218</v>
       </c>
       <c r="AJ39">
-        <v>0.3720970873786408</v>
+        <v>0.3624272517321017</v>
       </c>
       <c r="AK39">
-        <v>26.685</v>
+        <v>26.325</v>
       </c>
       <c r="AL39">
-        <v>10.41456310679612</v>
+        <v>10.13856812933025</v>
       </c>
       <c r="AM39">
-        <v>3.71757281553398</v>
+        <v>3.625150115473441</v>
       </c>
       <c r="AN39">
-        <v>42.18349514563107</v>
+        <v>42.64041570438799</v>
       </c>
       <c r="AO39">
-        <v>38.6747572815534</v>
+        <v>38.5729792147806</v>
       </c>
       <c r="AP39">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="AQ39">
-        <v>34.12135922330097</v>
+        <v>32.49445727482679</v>
       </c>
       <c r="AR39">
         <v>1</v>
@@ -7150,46 +7150,46 @@
         <v>197</v>
       </c>
       <c r="AD40">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="AE40">
         <v>11</v>
       </c>
       <c r="AF40">
-        <v>0.224</v>
+        <v>0.219</v>
       </c>
       <c r="AG40">
-        <v>0.3002912621359223</v>
+        <v>0.2944364896073903</v>
       </c>
       <c r="AH40">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AI40">
-        <v>0.1485339805825243</v>
+        <v>0.1430230946882218</v>
       </c>
       <c r="AJ40">
-        <v>0.3720970873786408</v>
+        <v>0.3624272517321017</v>
       </c>
       <c r="AK40">
-        <v>26.685</v>
+        <v>26.325</v>
       </c>
       <c r="AL40">
-        <v>10.41456310679612</v>
+        <v>10.13856812933025</v>
       </c>
       <c r="AM40">
-        <v>3.71757281553398</v>
+        <v>3.625150115473441</v>
       </c>
       <c r="AN40">
-        <v>42.18349514563107</v>
+        <v>42.64041570438799</v>
       </c>
       <c r="AO40">
-        <v>38.6747572815534</v>
+        <v>38.5729792147806</v>
       </c>
       <c r="AP40">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="AQ40">
-        <v>34.12135922330097</v>
+        <v>32.49445727482679</v>
       </c>
       <c r="AR40">
         <v>1</v>
@@ -7305,46 +7305,46 @@
         <v>197</v>
       </c>
       <c r="AD41">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="AE41">
         <v>11</v>
       </c>
       <c r="AF41">
-        <v>0.224</v>
+        <v>0.219</v>
       </c>
       <c r="AG41">
-        <v>0.3002912621359223</v>
+        <v>0.2944364896073903</v>
       </c>
       <c r="AH41">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AI41">
-        <v>0.1485339805825243</v>
+        <v>0.1430230946882218</v>
       </c>
       <c r="AJ41">
-        <v>0.3720970873786408</v>
+        <v>0.3624272517321017</v>
       </c>
       <c r="AK41">
-        <v>26.685</v>
+        <v>26.325</v>
       </c>
       <c r="AL41">
-        <v>10.41456310679612</v>
+        <v>10.13856812933025</v>
       </c>
       <c r="AM41">
-        <v>3.71757281553398</v>
+        <v>3.625150115473441</v>
       </c>
       <c r="AN41">
-        <v>42.18349514563107</v>
+        <v>42.64041570438799</v>
       </c>
       <c r="AO41">
-        <v>38.6747572815534</v>
+        <v>38.5729792147806</v>
       </c>
       <c r="AP41">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="AQ41">
-        <v>34.12135922330097</v>
+        <v>32.49445727482679</v>
       </c>
       <c r="AR41">
         <v>1</v>
@@ -7460,46 +7460,46 @@
         <v>198</v>
       </c>
       <c r="AD42">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AE42">
         <v>4</v>
       </c>
       <c r="AF42">
-        <v>0.239</v>
+        <v>0.248</v>
       </c>
       <c r="AG42">
-        <v>0.3099477124183007</v>
+        <v>0.3180128205128205</v>
       </c>
       <c r="AH42">
         <v>2.6</v>
       </c>
       <c r="AI42">
-        <v>0.1253529411764706</v>
+        <v>0.1293397435897436</v>
       </c>
       <c r="AJ42">
-        <v>0.3640065359477124</v>
+        <v>0.3768653846153847</v>
       </c>
       <c r="AK42">
-        <v>22.88</v>
+        <v>22.439</v>
       </c>
       <c r="AL42">
-        <v>11.79477124183007</v>
+        <v>11.58141025641026</v>
       </c>
       <c r="AM42">
-        <v>4.182418300653595</v>
+        <v>4.166794871794871</v>
       </c>
       <c r="AN42">
-        <v>40</v>
+        <v>40.66153846153846</v>
       </c>
       <c r="AO42">
-        <v>35.79019607843137</v>
+        <v>34.87884615384615</v>
       </c>
       <c r="AP42">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="AQ42">
-        <v>24.92745098039216</v>
+        <v>24.2724358974359</v>
       </c>
       <c r="AR42">
         <v>0</v>
@@ -7615,46 +7615,46 @@
         <v>197</v>
       </c>
       <c r="AD43">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="AE43">
         <v>11</v>
       </c>
       <c r="AF43">
-        <v>0.224</v>
+        <v>0.219</v>
       </c>
       <c r="AG43">
-        <v>0.3002912621359223</v>
+        <v>0.2944364896073903</v>
       </c>
       <c r="AH43">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AI43">
-        <v>0.1485339805825243</v>
+        <v>0.1430230946882218</v>
       </c>
       <c r="AJ43">
-        <v>0.3720970873786408</v>
+        <v>0.3624272517321017</v>
       </c>
       <c r="AK43">
-        <v>26.685</v>
+        <v>26.325</v>
       </c>
       <c r="AL43">
-        <v>10.41456310679612</v>
+        <v>10.13856812933025</v>
       </c>
       <c r="AM43">
-        <v>3.71757281553398</v>
+        <v>3.625150115473441</v>
       </c>
       <c r="AN43">
-        <v>42.18349514563107</v>
+        <v>42.64041570438799</v>
       </c>
       <c r="AO43">
-        <v>38.6747572815534</v>
+        <v>38.5729792147806</v>
       </c>
       <c r="AP43">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="AQ43">
-        <v>34.12135922330097</v>
+        <v>32.49445727482679</v>
       </c>
       <c r="AR43">
         <v>1</v>
@@ -7770,46 +7770,46 @@
         <v>197</v>
       </c>
       <c r="AD44">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="AE44">
         <v>11</v>
       </c>
       <c r="AF44">
-        <v>0.224</v>
+        <v>0.219</v>
       </c>
       <c r="AG44">
-        <v>0.3002912621359223</v>
+        <v>0.2944364896073903</v>
       </c>
       <c r="AH44">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AI44">
-        <v>0.1485339805825243</v>
+        <v>0.1430230946882218</v>
       </c>
       <c r="AJ44">
-        <v>0.3720970873786408</v>
+        <v>0.3624272517321017</v>
       </c>
       <c r="AK44">
-        <v>26.685</v>
+        <v>26.325</v>
       </c>
       <c r="AL44">
-        <v>10.41456310679612</v>
+        <v>10.13856812933025</v>
       </c>
       <c r="AM44">
-        <v>3.71757281553398</v>
+        <v>3.625150115473441</v>
       </c>
       <c r="AN44">
-        <v>42.18349514563107</v>
+        <v>42.64041570438799</v>
       </c>
       <c r="AO44">
-        <v>38.6747572815534</v>
+        <v>38.5729792147806</v>
       </c>
       <c r="AP44">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="AQ44">
-        <v>34.12135922330097</v>
+        <v>32.49445727482679</v>
       </c>
       <c r="AR44">
         <v>0</v>
@@ -7925,46 +7925,46 @@
         <v>197</v>
       </c>
       <c r="AD45">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="AE45">
         <v>11</v>
       </c>
       <c r="AF45">
-        <v>0.224</v>
+        <v>0.219</v>
       </c>
       <c r="AG45">
-        <v>0.3002912621359223</v>
+        <v>0.2944364896073903</v>
       </c>
       <c r="AH45">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AI45">
-        <v>0.1485339805825243</v>
+        <v>0.1430230946882218</v>
       </c>
       <c r="AJ45">
-        <v>0.3720970873786408</v>
+        <v>0.3624272517321017</v>
       </c>
       <c r="AK45">
-        <v>26.685</v>
+        <v>26.325</v>
       </c>
       <c r="AL45">
-        <v>10.41456310679612</v>
+        <v>10.13856812933025</v>
       </c>
       <c r="AM45">
-        <v>3.71757281553398</v>
+        <v>3.625150115473441</v>
       </c>
       <c r="AN45">
-        <v>42.18349514563107</v>
+        <v>42.64041570438799</v>
       </c>
       <c r="AO45">
-        <v>38.6747572815534</v>
+        <v>38.5729792147806</v>
       </c>
       <c r="AP45">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="AQ45">
-        <v>34.12135922330097</v>
+        <v>32.49445727482679</v>
       </c>
       <c r="AR45">
         <v>0</v>
@@ -8080,46 +8080,46 @@
         <v>197</v>
       </c>
       <c r="AD46">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="AE46">
         <v>11</v>
       </c>
       <c r="AF46">
-        <v>0.224</v>
+        <v>0.219</v>
       </c>
       <c r="AG46">
-        <v>0.3002912621359223</v>
+        <v>0.2944364896073903</v>
       </c>
       <c r="AH46">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AI46">
-        <v>0.1485339805825243</v>
+        <v>0.1430230946882218</v>
       </c>
       <c r="AJ46">
-        <v>0.3720970873786408</v>
+        <v>0.3624272517321017</v>
       </c>
       <c r="AK46">
-        <v>26.685</v>
+        <v>26.325</v>
       </c>
       <c r="AL46">
-        <v>10.41456310679612</v>
+        <v>10.13856812933025</v>
       </c>
       <c r="AM46">
-        <v>3.71757281553398</v>
+        <v>3.625150115473441</v>
       </c>
       <c r="AN46">
-        <v>42.18349514563107</v>
+        <v>42.64041570438799</v>
       </c>
       <c r="AO46">
-        <v>38.6747572815534</v>
+        <v>38.5729792147806</v>
       </c>
       <c r="AP46">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="AQ46">
-        <v>34.12135922330097</v>
+        <v>32.49445727482679</v>
       </c>
       <c r="AR46">
         <v>1</v>
@@ -8235,46 +8235,46 @@
         <v>198</v>
       </c>
       <c r="AD47">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AE47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF47">
-        <v>0.321</v>
+        <v>0.341</v>
       </c>
       <c r="AG47">
-        <v>0.36325</v>
+        <v>0.4002608695652174</v>
       </c>
       <c r="AH47">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI47">
-        <v>0.107</v>
+        <v>0.1673913043478261</v>
       </c>
       <c r="AJ47">
-        <v>0.42825</v>
+        <v>0.5085217391304349</v>
       </c>
       <c r="AK47">
-        <v>21.9</v>
+        <v>19.57</v>
       </c>
       <c r="AL47">
-        <v>6.225000000000001</v>
+        <v>6.482608695652174</v>
       </c>
       <c r="AM47">
-        <v>4.335</v>
+        <v>5.346521739130435</v>
       </c>
       <c r="AN47">
-        <v>41.575</v>
+        <v>53.2695652173913</v>
       </c>
       <c r="AO47">
-        <v>21.35</v>
+        <v>18.92608695652174</v>
       </c>
       <c r="AP47">
-        <v>12.5</v>
+        <v>23.9</v>
       </c>
       <c r="AQ47">
-        <v>39.6</v>
+        <v>36.83913043478261</v>
       </c>
       <c r="AR47">
         <v>1</v>
@@ -8390,46 +8390,46 @@
         <v>197</v>
       </c>
       <c r="AD48">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AE48">
         <v>1</v>
       </c>
       <c r="AF48">
-        <v>0.116</v>
+        <v>0.159</v>
       </c>
       <c r="AG48">
-        <v>0.1308461538461538</v>
+        <v>0.1798125</v>
       </c>
       <c r="AH48">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AI48">
-        <v>0.07684615384615384</v>
+        <v>0.078625</v>
       </c>
       <c r="AJ48">
-        <v>0.1924615384615385</v>
+        <v>0.2373125</v>
       </c>
       <c r="AK48">
-        <v>28.877</v>
+        <v>26.575</v>
       </c>
       <c r="AL48">
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="AM48">
-        <v>2.070769230769231</v>
+        <v>2.13375</v>
       </c>
       <c r="AN48">
-        <v>65.11538461538461</v>
+        <v>65.26875000000001</v>
       </c>
       <c r="AO48">
-        <v>24.12307692307692</v>
+        <v>21.7</v>
       </c>
       <c r="AP48">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AQ48">
-        <v>40.38461538461539</v>
+        <v>34.7375</v>
       </c>
       <c r="AR48">
         <v>1</v>
@@ -8545,46 +8545,46 @@
         <v>198</v>
       </c>
       <c r="AD49">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AE49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF49">
-        <v>0.321</v>
+        <v>0.341</v>
       </c>
       <c r="AG49">
-        <v>0.36325</v>
+        <v>0.4002608695652174</v>
       </c>
       <c r="AH49">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI49">
-        <v>0.107</v>
+        <v>0.1673913043478261</v>
       </c>
       <c r="AJ49">
-        <v>0.42825</v>
+        <v>0.5085217391304349</v>
       </c>
       <c r="AK49">
-        <v>21.9</v>
+        <v>19.57</v>
       </c>
       <c r="AL49">
-        <v>6.225000000000001</v>
+        <v>6.482608695652174</v>
       </c>
       <c r="AM49">
-        <v>4.335</v>
+        <v>5.346521739130435</v>
       </c>
       <c r="AN49">
-        <v>41.575</v>
+        <v>53.2695652173913</v>
       </c>
       <c r="AO49">
-        <v>21.35</v>
+        <v>18.92608695652174</v>
       </c>
       <c r="AP49">
-        <v>12.5</v>
+        <v>23.9</v>
       </c>
       <c r="AQ49">
-        <v>39.6</v>
+        <v>36.83913043478261</v>
       </c>
       <c r="AR49">
         <v>0</v>
@@ -8700,46 +8700,46 @@
         <v>198</v>
       </c>
       <c r="AD50">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AE50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF50">
-        <v>0.321</v>
+        <v>0.341</v>
       </c>
       <c r="AG50">
-        <v>0.36325</v>
+        <v>0.4002608695652174</v>
       </c>
       <c r="AH50">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI50">
-        <v>0.107</v>
+        <v>0.1673913043478261</v>
       </c>
       <c r="AJ50">
-        <v>0.42825</v>
+        <v>0.5085217391304349</v>
       </c>
       <c r="AK50">
-        <v>21.9</v>
+        <v>19.57</v>
       </c>
       <c r="AL50">
-        <v>6.225000000000001</v>
+        <v>6.482608695652174</v>
       </c>
       <c r="AM50">
-        <v>4.335</v>
+        <v>5.346521739130435</v>
       </c>
       <c r="AN50">
-        <v>41.575</v>
+        <v>53.2695652173913</v>
       </c>
       <c r="AO50">
-        <v>21.35</v>
+        <v>18.92608695652174</v>
       </c>
       <c r="AP50">
-        <v>12.5</v>
+        <v>23.9</v>
       </c>
       <c r="AQ50">
-        <v>39.6</v>
+        <v>36.83913043478261</v>
       </c>
       <c r="AR50">
         <v>0</v>
@@ -8855,46 +8855,46 @@
         <v>197</v>
       </c>
       <c r="AD51">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AE51">
         <v>1</v>
       </c>
       <c r="AF51">
-        <v>0.116</v>
+        <v>0.159</v>
       </c>
       <c r="AG51">
-        <v>0.1308461538461538</v>
+        <v>0.1798125</v>
       </c>
       <c r="AH51">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AI51">
-        <v>0.07684615384615384</v>
+        <v>0.078625</v>
       </c>
       <c r="AJ51">
-        <v>0.1924615384615385</v>
+        <v>0.2373125</v>
       </c>
       <c r="AK51">
-        <v>28.877</v>
+        <v>26.575</v>
       </c>
       <c r="AL51">
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="AM51">
-        <v>2.070769230769231</v>
+        <v>2.13375</v>
       </c>
       <c r="AN51">
-        <v>65.11538461538461</v>
+        <v>65.26875000000001</v>
       </c>
       <c r="AO51">
-        <v>24.12307692307692</v>
+        <v>21.7</v>
       </c>
       <c r="AP51">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AQ51">
-        <v>40.38461538461539</v>
+        <v>34.7375</v>
       </c>
       <c r="AR51">
         <v>0</v>
@@ -9010,46 +9010,46 @@
         <v>198</v>
       </c>
       <c r="AD52">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AE52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF52">
-        <v>0.321</v>
+        <v>0.341</v>
       </c>
       <c r="AG52">
-        <v>0.36325</v>
+        <v>0.4002608695652174</v>
       </c>
       <c r="AH52">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI52">
-        <v>0.107</v>
+        <v>0.1673913043478261</v>
       </c>
       <c r="AJ52">
-        <v>0.42825</v>
+        <v>0.5085217391304349</v>
       </c>
       <c r="AK52">
-        <v>21.9</v>
+        <v>19.57</v>
       </c>
       <c r="AL52">
-        <v>6.225000000000001</v>
+        <v>6.482608695652174</v>
       </c>
       <c r="AM52">
-        <v>4.335</v>
+        <v>5.346521739130435</v>
       </c>
       <c r="AN52">
-        <v>41.575</v>
+        <v>53.2695652173913</v>
       </c>
       <c r="AO52">
-        <v>21.35</v>
+        <v>18.92608695652174</v>
       </c>
       <c r="AP52">
-        <v>12.5</v>
+        <v>23.9</v>
       </c>
       <c r="AQ52">
-        <v>39.6</v>
+        <v>36.83913043478261</v>
       </c>
       <c r="AR52">
         <v>1</v>
@@ -9165,46 +9165,46 @@
         <v>197</v>
       </c>
       <c r="AD53">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AE53">
         <v>1</v>
       </c>
       <c r="AF53">
-        <v>0.116</v>
+        <v>0.159</v>
       </c>
       <c r="AG53">
-        <v>0.1308461538461538</v>
+        <v>0.1798125</v>
       </c>
       <c r="AH53">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AI53">
-        <v>0.07684615384615384</v>
+        <v>0.078625</v>
       </c>
       <c r="AJ53">
-        <v>0.1924615384615385</v>
+        <v>0.2373125</v>
       </c>
       <c r="AK53">
-        <v>28.877</v>
+        <v>26.575</v>
       </c>
       <c r="AL53">
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="AM53">
-        <v>2.070769230769231</v>
+        <v>2.13375</v>
       </c>
       <c r="AN53">
-        <v>65.11538461538461</v>
+        <v>65.26875000000001</v>
       </c>
       <c r="AO53">
-        <v>24.12307692307692</v>
+        <v>21.7</v>
       </c>
       <c r="AP53">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AQ53">
-        <v>40.38461538461539</v>
+        <v>34.7375</v>
       </c>
       <c r="AR53">
         <v>1</v>
@@ -9320,46 +9320,46 @@
         <v>197</v>
       </c>
       <c r="AD54">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AE54">
         <v>1</v>
       </c>
       <c r="AF54">
-        <v>0.116</v>
+        <v>0.159</v>
       </c>
       <c r="AG54">
-        <v>0.1308461538461538</v>
+        <v>0.1798125</v>
       </c>
       <c r="AH54">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AI54">
-        <v>0.07684615384615384</v>
+        <v>0.078625</v>
       </c>
       <c r="AJ54">
-        <v>0.1924615384615385</v>
+        <v>0.2373125</v>
       </c>
       <c r="AK54">
-        <v>28.877</v>
+        <v>26.575</v>
       </c>
       <c r="AL54">
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="AM54">
-        <v>2.070769230769231</v>
+        <v>2.13375</v>
       </c>
       <c r="AN54">
-        <v>65.11538461538461</v>
+        <v>65.26875000000001</v>
       </c>
       <c r="AO54">
-        <v>24.12307692307692</v>
+        <v>21.7</v>
       </c>
       <c r="AP54">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AQ54">
-        <v>40.38461538461539</v>
+        <v>34.7375</v>
       </c>
       <c r="AR54">
         <v>0</v>
@@ -9475,46 +9475,46 @@
         <v>197</v>
       </c>
       <c r="AD55">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="AE55">
         <v>7</v>
       </c>
       <c r="AF55">
-        <v>0.268</v>
+        <v>0.265</v>
       </c>
       <c r="AG55">
-        <v>0.3334358974358974</v>
+        <v>0.3312608695652174</v>
       </c>
       <c r="AH55">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AI55">
-        <v>0.189</v>
+        <v>0.1897826086956522</v>
       </c>
       <c r="AJ55">
-        <v>0.4566410256410257</v>
+        <v>0.4551304347826087</v>
       </c>
       <c r="AK55">
-        <v>21.146</v>
+        <v>21.704</v>
       </c>
       <c r="AL55">
-        <v>7.092307692307693</v>
+        <v>6.860869565217391</v>
       </c>
       <c r="AM55">
-        <v>4.700769230769231</v>
+        <v>4.52</v>
       </c>
       <c r="AN55">
-        <v>44.25641025641026</v>
+        <v>43.97826086956522</v>
       </c>
       <c r="AO55">
-        <v>39.54615384615384</v>
+        <v>39.35217391304347</v>
       </c>
       <c r="AP55">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ55">
-        <v>29.4974358974359</v>
+        <v>28.69130434782609</v>
       </c>
       <c r="AR55">
         <v>1</v>
@@ -9630,46 +9630,46 @@
         <v>198</v>
       </c>
       <c r="AD56">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="AE56">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF56">
-        <v>0.297</v>
+        <v>0.285</v>
       </c>
       <c r="AG56">
-        <v>0.3796735751295337</v>
+        <v>0.3733428571428571</v>
       </c>
       <c r="AH56">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI56">
-        <v>0.2208911917098446</v>
+        <v>0.2204571428571429</v>
       </c>
       <c r="AJ56">
-        <v>0.5178652849740933</v>
+        <v>0.5056</v>
       </c>
       <c r="AK56">
-        <v>14.527</v>
+        <v>14.774</v>
       </c>
       <c r="AL56">
-        <v>9.830569948186527</v>
+        <v>10.47142857142857</v>
       </c>
       <c r="AM56">
-        <v>5.647668393782384</v>
+        <v>5.762285714285714</v>
       </c>
       <c r="AN56">
-        <v>42.07098445595855</v>
+        <v>40.32</v>
       </c>
       <c r="AO56">
-        <v>40.35699481865285</v>
+        <v>42.73142857142857</v>
       </c>
       <c r="AP56">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ56">
-        <v>32.6580310880829</v>
+        <v>31.78857142857143</v>
       </c>
       <c r="AR56">
         <v>1</v>
@@ -9785,46 +9785,46 @@
         <v>198</v>
       </c>
       <c r="AD57">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="AE57">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF57">
-        <v>0.297</v>
+        <v>0.285</v>
       </c>
       <c r="AG57">
-        <v>0.3796735751295337</v>
+        <v>0.3733428571428571</v>
       </c>
       <c r="AH57">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI57">
-        <v>0.2208911917098446</v>
+        <v>0.2204571428571429</v>
       </c>
       <c r="AJ57">
-        <v>0.5178652849740933</v>
+        <v>0.5056</v>
       </c>
       <c r="AK57">
-        <v>14.527</v>
+        <v>14.774</v>
       </c>
       <c r="AL57">
-        <v>9.830569948186527</v>
+        <v>10.47142857142857</v>
       </c>
       <c r="AM57">
-        <v>5.647668393782384</v>
+        <v>5.762285714285714</v>
       </c>
       <c r="AN57">
-        <v>42.07098445595855</v>
+        <v>40.32</v>
       </c>
       <c r="AO57">
-        <v>40.35699481865285</v>
+        <v>42.73142857142857</v>
       </c>
       <c r="AP57">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ57">
-        <v>32.6580310880829</v>
+        <v>31.78857142857143</v>
       </c>
       <c r="AR57">
         <v>0</v>
@@ -9940,46 +9940,46 @@
         <v>198</v>
       </c>
       <c r="AD58">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="AE58">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF58">
-        <v>0.297</v>
+        <v>0.285</v>
       </c>
       <c r="AG58">
-        <v>0.3796735751295337</v>
+        <v>0.3733428571428571</v>
       </c>
       <c r="AH58">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI58">
-        <v>0.2208911917098446</v>
+        <v>0.2204571428571429</v>
       </c>
       <c r="AJ58">
-        <v>0.5178652849740933</v>
+        <v>0.5056</v>
       </c>
       <c r="AK58">
-        <v>14.527</v>
+        <v>14.774</v>
       </c>
       <c r="AL58">
-        <v>9.830569948186527</v>
+        <v>10.47142857142857</v>
       </c>
       <c r="AM58">
-        <v>5.647668393782384</v>
+        <v>5.762285714285714</v>
       </c>
       <c r="AN58">
-        <v>42.07098445595855</v>
+        <v>40.32</v>
       </c>
       <c r="AO58">
-        <v>40.35699481865285</v>
+        <v>42.73142857142857</v>
       </c>
       <c r="AP58">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ58">
-        <v>32.6580310880829</v>
+        <v>31.78857142857143</v>
       </c>
       <c r="AR58">
         <v>0</v>
@@ -10095,46 +10095,46 @@
         <v>198</v>
       </c>
       <c r="AD59">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="AE59">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF59">
-        <v>0.297</v>
+        <v>0.285</v>
       </c>
       <c r="AG59">
-        <v>0.3796735751295337</v>
+        <v>0.3733428571428571</v>
       </c>
       <c r="AH59">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI59">
-        <v>0.2208911917098446</v>
+        <v>0.2204571428571429</v>
       </c>
       <c r="AJ59">
-        <v>0.5178652849740933</v>
+        <v>0.5056</v>
       </c>
       <c r="AK59">
-        <v>14.527</v>
+        <v>14.774</v>
       </c>
       <c r="AL59">
-        <v>9.830569948186527</v>
+        <v>10.47142857142857</v>
       </c>
       <c r="AM59">
-        <v>5.647668393782384</v>
+        <v>5.762285714285714</v>
       </c>
       <c r="AN59">
-        <v>42.07098445595855</v>
+        <v>40.32</v>
       </c>
       <c r="AO59">
-        <v>40.35699481865285</v>
+        <v>42.73142857142857</v>
       </c>
       <c r="AP59">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ59">
-        <v>32.6580310880829</v>
+        <v>31.78857142857143</v>
       </c>
       <c r="AR59">
         <v>1</v>
@@ -10250,46 +10250,46 @@
         <v>197</v>
       </c>
       <c r="AD60">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="AE60">
         <v>7</v>
       </c>
       <c r="AF60">
-        <v>0.268</v>
+        <v>0.265</v>
       </c>
       <c r="AG60">
-        <v>0.3334358974358974</v>
+        <v>0.3312608695652174</v>
       </c>
       <c r="AH60">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AI60">
-        <v>0.189</v>
+        <v>0.1897826086956522</v>
       </c>
       <c r="AJ60">
-        <v>0.4566410256410257</v>
+        <v>0.4551304347826087</v>
       </c>
       <c r="AK60">
-        <v>21.146</v>
+        <v>21.704</v>
       </c>
       <c r="AL60">
-        <v>7.092307692307693</v>
+        <v>6.860869565217391</v>
       </c>
       <c r="AM60">
-        <v>4.700769230769231</v>
+        <v>4.52</v>
       </c>
       <c r="AN60">
-        <v>44.25641025641026</v>
+        <v>43.97826086956522</v>
       </c>
       <c r="AO60">
-        <v>39.54615384615384</v>
+        <v>39.35217391304347</v>
       </c>
       <c r="AP60">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ60">
-        <v>29.4974358974359</v>
+        <v>28.69130434782609</v>
       </c>
       <c r="AR60">
         <v>1</v>
@@ -10405,46 +10405,46 @@
         <v>198</v>
       </c>
       <c r="AD61">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="AE61">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF61">
-        <v>0.297</v>
+        <v>0.285</v>
       </c>
       <c r="AG61">
-        <v>0.3796735751295337</v>
+        <v>0.3733428571428571</v>
       </c>
       <c r="AH61">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI61">
-        <v>0.2208911917098446</v>
+        <v>0.2204571428571429</v>
       </c>
       <c r="AJ61">
-        <v>0.5178652849740933</v>
+        <v>0.5056</v>
       </c>
       <c r="AK61">
-        <v>14.527</v>
+        <v>14.774</v>
       </c>
       <c r="AL61">
-        <v>9.830569948186527</v>
+        <v>10.47142857142857</v>
       </c>
       <c r="AM61">
-        <v>5.647668393782384</v>
+        <v>5.762285714285714</v>
       </c>
       <c r="AN61">
-        <v>42.07098445595855</v>
+        <v>40.32</v>
       </c>
       <c r="AO61">
-        <v>40.35699481865285</v>
+        <v>42.73142857142857</v>
       </c>
       <c r="AP61">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ61">
-        <v>32.6580310880829</v>
+        <v>31.78857142857143</v>
       </c>
       <c r="AR61">
         <v>1</v>
@@ -10560,46 +10560,46 @@
         <v>198</v>
       </c>
       <c r="AD62">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="AE62">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF62">
-        <v>0.297</v>
+        <v>0.285</v>
       </c>
       <c r="AG62">
-        <v>0.3796735751295337</v>
+        <v>0.3733428571428571</v>
       </c>
       <c r="AH62">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI62">
-        <v>0.2208911917098446</v>
+        <v>0.2204571428571429</v>
       </c>
       <c r="AJ62">
-        <v>0.5178652849740933</v>
+        <v>0.5056</v>
       </c>
       <c r="AK62">
-        <v>14.527</v>
+        <v>14.774</v>
       </c>
       <c r="AL62">
-        <v>9.830569948186527</v>
+        <v>10.47142857142857</v>
       </c>
       <c r="AM62">
-        <v>5.647668393782384</v>
+        <v>5.762285714285714</v>
       </c>
       <c r="AN62">
-        <v>42.07098445595855</v>
+        <v>40.32</v>
       </c>
       <c r="AO62">
-        <v>40.35699481865285</v>
+        <v>42.73142857142857</v>
       </c>
       <c r="AP62">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ62">
-        <v>32.6580310880829</v>
+        <v>31.78857142857143</v>
       </c>
       <c r="AR62">
         <v>1</v>
@@ -10715,46 +10715,46 @@
         <v>198</v>
       </c>
       <c r="AD63">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="AE63">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF63">
-        <v>0.297</v>
+        <v>0.285</v>
       </c>
       <c r="AG63">
-        <v>0.3796735751295337</v>
+        <v>0.3733428571428571</v>
       </c>
       <c r="AH63">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI63">
-        <v>0.2208911917098446</v>
+        <v>0.2204571428571429</v>
       </c>
       <c r="AJ63">
-        <v>0.5178652849740933</v>
+        <v>0.5056</v>
       </c>
       <c r="AK63">
-        <v>14.527</v>
+        <v>14.774</v>
       </c>
       <c r="AL63">
-        <v>9.830569948186527</v>
+        <v>10.47142857142857</v>
       </c>
       <c r="AM63">
-        <v>5.647668393782384</v>
+        <v>5.762285714285714</v>
       </c>
       <c r="AN63">
-        <v>42.07098445595855</v>
+        <v>40.32</v>
       </c>
       <c r="AO63">
-        <v>40.35699481865285</v>
+        <v>42.73142857142857</v>
       </c>
       <c r="AP63">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ63">
-        <v>32.6580310880829</v>
+        <v>31.78857142857143</v>
       </c>
       <c r="AR63">
         <v>1</v>
@@ -10870,7 +10870,7 @@
         <v>197</v>
       </c>
       <c r="AD64">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="AE64">
         <v>6</v>
@@ -10879,37 +10879,37 @@
         <v>0.257</v>
       </c>
       <c r="AG64">
-        <v>0.373472</v>
+        <v>0.3683381294964029</v>
       </c>
       <c r="AH64">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AI64">
-        <v>0.248776</v>
+        <v>0.2320287769784172</v>
       </c>
       <c r="AJ64">
-        <v>0.5062</v>
+        <v>0.488705035971223</v>
       </c>
       <c r="AK64">
-        <v>18.394</v>
+        <v>19.412</v>
       </c>
       <c r="AL64">
-        <v>8.808</v>
+        <v>8.610791366906476</v>
       </c>
       <c r="AM64">
-        <v>6.063359999999999</v>
+        <v>5.693381294964029</v>
       </c>
       <c r="AN64">
-        <v>50</v>
+        <v>52.26618705035972</v>
       </c>
       <c r="AO64">
-        <v>31.6024</v>
+        <v>29.93021582733813</v>
       </c>
       <c r="AP64">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AQ64">
-        <v>30.568</v>
+        <v>31.30647482014389</v>
       </c>
       <c r="AR64">
         <v>1</v>
@@ -11025,46 +11025,46 @@
         <v>198</v>
       </c>
       <c r="AD65">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="AE65">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF65">
-        <v>0.246</v>
+        <v>0.25</v>
       </c>
       <c r="AG65">
-        <v>0.3635</v>
+        <v>0.3670335195530726</v>
       </c>
       <c r="AH65">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AI65">
-        <v>0.2035</v>
+        <v>0.2105810055865922</v>
       </c>
       <c r="AJ65">
-        <v>0.449</v>
+        <v>0.4608435754189945</v>
       </c>
       <c r="AK65">
-        <v>18.2</v>
+        <v>17.863</v>
       </c>
       <c r="AL65">
-        <v>15.25</v>
+        <v>14.50167597765363</v>
       </c>
       <c r="AM65">
-        <v>6.449999999999999</v>
+        <v>6.559162011173184</v>
       </c>
       <c r="AN65">
-        <v>29.7</v>
+        <v>29.37541899441341</v>
       </c>
       <c r="AO65">
-        <v>51.40000000000001</v>
+        <v>51.33687150837989</v>
       </c>
       <c r="AP65">
-        <v>14</v>
+        <v>14.7</v>
       </c>
       <c r="AQ65">
-        <v>32.15</v>
+        <v>31.65754189944134</v>
       </c>
       <c r="AR65">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>197</v>
       </c>
       <c r="AD66">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="AE66">
         <v>6</v>
@@ -11189,37 +11189,37 @@
         <v>0.257</v>
       </c>
       <c r="AG66">
-        <v>0.373472</v>
+        <v>0.3683381294964029</v>
       </c>
       <c r="AH66">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AI66">
-        <v>0.248776</v>
+        <v>0.2320287769784172</v>
       </c>
       <c r="AJ66">
-        <v>0.5062</v>
+        <v>0.488705035971223</v>
       </c>
       <c r="AK66">
-        <v>18.394</v>
+        <v>19.412</v>
       </c>
       <c r="AL66">
-        <v>8.808</v>
+        <v>8.610791366906476</v>
       </c>
       <c r="AM66">
-        <v>6.063359999999999</v>
+        <v>5.693381294964029</v>
       </c>
       <c r="AN66">
-        <v>50</v>
+        <v>52.26618705035972</v>
       </c>
       <c r="AO66">
-        <v>31.6024</v>
+        <v>29.93021582733813</v>
       </c>
       <c r="AP66">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AQ66">
-        <v>30.568</v>
+        <v>31.30647482014389</v>
       </c>
       <c r="AR66">
         <v>1</v>
@@ -11335,7 +11335,7 @@
         <v>197</v>
       </c>
       <c r="AD67">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="AE67">
         <v>6</v>
@@ -11344,37 +11344,37 @@
         <v>0.257</v>
       </c>
       <c r="AG67">
-        <v>0.373472</v>
+        <v>0.3683381294964029</v>
       </c>
       <c r="AH67">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AI67">
-        <v>0.248776</v>
+        <v>0.2320287769784172</v>
       </c>
       <c r="AJ67">
-        <v>0.5062</v>
+        <v>0.488705035971223</v>
       </c>
       <c r="AK67">
-        <v>18.394</v>
+        <v>19.412</v>
       </c>
       <c r="AL67">
-        <v>8.808</v>
+        <v>8.610791366906476</v>
       </c>
       <c r="AM67">
-        <v>6.063359999999999</v>
+        <v>5.693381294964029</v>
       </c>
       <c r="AN67">
-        <v>50</v>
+        <v>52.26618705035972</v>
       </c>
       <c r="AO67">
-        <v>31.6024</v>
+        <v>29.93021582733813</v>
       </c>
       <c r="AP67">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AQ67">
-        <v>30.568</v>
+        <v>31.30647482014389</v>
       </c>
       <c r="AR67">
         <v>0</v>
@@ -11490,46 +11490,46 @@
         <v>198</v>
       </c>
       <c r="AD68">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="AE68">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF68">
-        <v>0.246</v>
+        <v>0.25</v>
       </c>
       <c r="AG68">
-        <v>0.3635</v>
+        <v>0.3670335195530726</v>
       </c>
       <c r="AH68">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AI68">
-        <v>0.2035</v>
+        <v>0.2105810055865922</v>
       </c>
       <c r="AJ68">
-        <v>0.449</v>
+        <v>0.4608435754189945</v>
       </c>
       <c r="AK68">
-        <v>18.2</v>
+        <v>17.863</v>
       </c>
       <c r="AL68">
-        <v>15.25</v>
+        <v>14.50167597765363</v>
       </c>
       <c r="AM68">
-        <v>6.449999999999999</v>
+        <v>6.559162011173184</v>
       </c>
       <c r="AN68">
-        <v>29.7</v>
+        <v>29.37541899441341</v>
       </c>
       <c r="AO68">
-        <v>51.40000000000001</v>
+        <v>51.33687150837989</v>
       </c>
       <c r="AP68">
-        <v>14</v>
+        <v>14.7</v>
       </c>
       <c r="AQ68">
-        <v>32.15</v>
+        <v>31.65754189944134</v>
       </c>
       <c r="AR68">
         <v>0</v>
@@ -11645,46 +11645,46 @@
         <v>198</v>
       </c>
       <c r="AD69">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="AE69">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF69">
-        <v>0.246</v>
+        <v>0.25</v>
       </c>
       <c r="AG69">
-        <v>0.3635</v>
+        <v>0.3670335195530726</v>
       </c>
       <c r="AH69">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AI69">
-        <v>0.2035</v>
+        <v>0.2105810055865922</v>
       </c>
       <c r="AJ69">
-        <v>0.449</v>
+        <v>0.4608435754189945</v>
       </c>
       <c r="AK69">
-        <v>18.2</v>
+        <v>17.863</v>
       </c>
       <c r="AL69">
-        <v>15.25</v>
+        <v>14.50167597765363</v>
       </c>
       <c r="AM69">
-        <v>6.449999999999999</v>
+        <v>6.559162011173184</v>
       </c>
       <c r="AN69">
-        <v>29.7</v>
+        <v>29.37541899441341</v>
       </c>
       <c r="AO69">
-        <v>51.40000000000001</v>
+        <v>51.33687150837989</v>
       </c>
       <c r="AP69">
-        <v>14</v>
+        <v>14.7</v>
       </c>
       <c r="AQ69">
-        <v>32.15</v>
+        <v>31.65754189944134</v>
       </c>
       <c r="AR69">
         <v>0</v>
@@ -11800,7 +11800,7 @@
         <v>197</v>
       </c>
       <c r="AD70">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="AE70">
         <v>6</v>
@@ -11809,37 +11809,37 @@
         <v>0.257</v>
       </c>
       <c r="AG70">
-        <v>0.373472</v>
+        <v>0.3683381294964029</v>
       </c>
       <c r="AH70">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AI70">
-        <v>0.248776</v>
+        <v>0.2320287769784172</v>
       </c>
       <c r="AJ70">
-        <v>0.5062</v>
+        <v>0.488705035971223</v>
       </c>
       <c r="AK70">
-        <v>18.394</v>
+        <v>19.412</v>
       </c>
       <c r="AL70">
-        <v>8.808</v>
+        <v>8.610791366906476</v>
       </c>
       <c r="AM70">
-        <v>6.063359999999999</v>
+        <v>5.693381294964029</v>
       </c>
       <c r="AN70">
-        <v>50</v>
+        <v>52.26618705035972</v>
       </c>
       <c r="AO70">
-        <v>31.6024</v>
+        <v>29.93021582733813</v>
       </c>
       <c r="AP70">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AQ70">
-        <v>30.568</v>
+        <v>31.30647482014389</v>
       </c>
       <c r="AR70">
         <v>1</v>
@@ -11955,46 +11955,46 @@
         <v>198</v>
       </c>
       <c r="AD71">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="AE71">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF71">
-        <v>0.246</v>
+        <v>0.25</v>
       </c>
       <c r="AG71">
-        <v>0.3635</v>
+        <v>0.3670335195530726</v>
       </c>
       <c r="AH71">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AI71">
-        <v>0.2035</v>
+        <v>0.2105810055865922</v>
       </c>
       <c r="AJ71">
-        <v>0.449</v>
+        <v>0.4608435754189945</v>
       </c>
       <c r="AK71">
-        <v>18.2</v>
+        <v>17.863</v>
       </c>
       <c r="AL71">
-        <v>15.25</v>
+        <v>14.50167597765363</v>
       </c>
       <c r="AM71">
-        <v>6.449999999999999</v>
+        <v>6.559162011173184</v>
       </c>
       <c r="AN71">
-        <v>29.7</v>
+        <v>29.37541899441341</v>
       </c>
       <c r="AO71">
-        <v>51.40000000000001</v>
+        <v>51.33687150837989</v>
       </c>
       <c r="AP71">
-        <v>14</v>
+        <v>14.7</v>
       </c>
       <c r="AQ71">
-        <v>32.15</v>
+        <v>31.65754189944134</v>
       </c>
       <c r="AR71">
         <v>1</v>
@@ -12110,7 +12110,7 @@
         <v>197</v>
       </c>
       <c r="AD72">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="AE72">
         <v>6</v>
@@ -12119,37 +12119,37 @@
         <v>0.257</v>
       </c>
       <c r="AG72">
-        <v>0.373472</v>
+        <v>0.3683381294964029</v>
       </c>
       <c r="AH72">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AI72">
-        <v>0.248776</v>
+        <v>0.2320287769784172</v>
       </c>
       <c r="AJ72">
-        <v>0.5062</v>
+        <v>0.488705035971223</v>
       </c>
       <c r="AK72">
-        <v>18.394</v>
+        <v>19.412</v>
       </c>
       <c r="AL72">
-        <v>8.808</v>
+        <v>8.610791366906476</v>
       </c>
       <c r="AM72">
-        <v>6.063359999999999</v>
+        <v>5.693381294964029</v>
       </c>
       <c r="AN72">
-        <v>50</v>
+        <v>52.26618705035972</v>
       </c>
       <c r="AO72">
-        <v>31.6024</v>
+        <v>29.93021582733813</v>
       </c>
       <c r="AP72">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AQ72">
-        <v>30.568</v>
+        <v>31.30647482014389</v>
       </c>
       <c r="AR72">
         <v>1</v>
@@ -12265,46 +12265,46 @@
         <v>198</v>
       </c>
       <c r="AD73">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="AE73">
         <v>0</v>
       </c>
       <c r="AF73">
-        <v>0.14</v>
+        <v>0.129</v>
       </c>
       <c r="AG73">
-        <v>0.23</v>
+        <v>0.201</v>
       </c>
       <c r="AH73">
         <v>0</v>
       </c>
       <c r="AI73">
-        <v>0.01999999999999999</v>
+        <v>0.01399999999999998</v>
       </c>
       <c r="AJ73">
-        <v>0.16</v>
+        <v>0.143</v>
       </c>
       <c r="AK73">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="AL73">
-        <v>15</v>
+        <v>12.3</v>
       </c>
       <c r="AM73">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AN73">
-        <v>45.2</v>
+        <v>47.8</v>
       </c>
       <c r="AO73">
-        <v>41.9</v>
+        <v>39.1</v>
       </c>
       <c r="AP73">
         <v>0</v>
       </c>
       <c r="AQ73">
-        <v>15.6</v>
+        <v>23.4</v>
       </c>
       <c r="AR73">
         <v>0</v>
@@ -12420,46 +12420,46 @@
         <v>198</v>
       </c>
       <c r="AD74">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="AE74">
         <v>0</v>
       </c>
       <c r="AF74">
-        <v>0.14</v>
+        <v>0.129</v>
       </c>
       <c r="AG74">
-        <v>0.23</v>
+        <v>0.201</v>
       </c>
       <c r="AH74">
         <v>0</v>
       </c>
       <c r="AI74">
-        <v>0.01999999999999999</v>
+        <v>0.01399999999999998</v>
       </c>
       <c r="AJ74">
-        <v>0.16</v>
+        <v>0.143</v>
       </c>
       <c r="AK74">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="AL74">
-        <v>15</v>
+        <v>12.3</v>
       </c>
       <c r="AM74">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AN74">
-        <v>45.2</v>
+        <v>47.8</v>
       </c>
       <c r="AO74">
-        <v>41.9</v>
+        <v>39.1</v>
       </c>
       <c r="AP74">
         <v>0</v>
       </c>
       <c r="AQ74">
-        <v>15.6</v>
+        <v>23.4</v>
       </c>
       <c r="AR74">
         <v>1</v>
@@ -12575,46 +12575,46 @@
         <v>198</v>
       </c>
       <c r="AD75">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="AE75">
         <v>0</v>
       </c>
       <c r="AF75">
-        <v>0.14</v>
+        <v>0.129</v>
       </c>
       <c r="AG75">
-        <v>0.23</v>
+        <v>0.201</v>
       </c>
       <c r="AH75">
         <v>0</v>
       </c>
       <c r="AI75">
-        <v>0.01999999999999999</v>
+        <v>0.01399999999999998</v>
       </c>
       <c r="AJ75">
-        <v>0.16</v>
+        <v>0.143</v>
       </c>
       <c r="AK75">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="AL75">
-        <v>15</v>
+        <v>12.3</v>
       </c>
       <c r="AM75">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AN75">
-        <v>45.2</v>
+        <v>47.8</v>
       </c>
       <c r="AO75">
-        <v>41.9</v>
+        <v>39.1</v>
       </c>
       <c r="AP75">
         <v>0</v>
       </c>
       <c r="AQ75">
-        <v>15.6</v>
+        <v>23.4</v>
       </c>
       <c r="AR75">
         <v>1</v>
@@ -12730,46 +12730,46 @@
         <v>198</v>
       </c>
       <c r="AD76">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="AE76">
         <v>0</v>
       </c>
       <c r="AF76">
-        <v>0.14</v>
+        <v>0.129</v>
       </c>
       <c r="AG76">
-        <v>0.23</v>
+        <v>0.201</v>
       </c>
       <c r="AH76">
         <v>0</v>
       </c>
       <c r="AI76">
-        <v>0.01999999999999999</v>
+        <v>0.01399999999999998</v>
       </c>
       <c r="AJ76">
-        <v>0.16</v>
+        <v>0.143</v>
       </c>
       <c r="AK76">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="AL76">
-        <v>15</v>
+        <v>12.3</v>
       </c>
       <c r="AM76">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AN76">
-        <v>45.2</v>
+        <v>47.8</v>
       </c>
       <c r="AO76">
-        <v>41.9</v>
+        <v>39.1</v>
       </c>
       <c r="AP76">
         <v>0</v>
       </c>
       <c r="AQ76">
-        <v>15.6</v>
+        <v>23.4</v>
       </c>
       <c r="AR76">
         <v>1</v>
@@ -12885,46 +12885,46 @@
         <v>198</v>
       </c>
       <c r="AD77">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="AE77">
         <v>0</v>
       </c>
       <c r="AF77">
-        <v>0.14</v>
+        <v>0.129</v>
       </c>
       <c r="AG77">
-        <v>0.23</v>
+        <v>0.201</v>
       </c>
       <c r="AH77">
         <v>0</v>
       </c>
       <c r="AI77">
-        <v>0.01999999999999999</v>
+        <v>0.01399999999999998</v>
       </c>
       <c r="AJ77">
-        <v>0.16</v>
+        <v>0.143</v>
       </c>
       <c r="AK77">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="AL77">
-        <v>15</v>
+        <v>12.3</v>
       </c>
       <c r="AM77">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AN77">
-        <v>45.2</v>
+        <v>47.8</v>
       </c>
       <c r="AO77">
-        <v>41.9</v>
+        <v>39.1</v>
       </c>
       <c r="AP77">
         <v>0</v>
       </c>
       <c r="AQ77">
-        <v>15.6</v>
+        <v>23.4</v>
       </c>
       <c r="AR77">
         <v>0</v>
@@ -13040,46 +13040,46 @@
         <v>198</v>
       </c>
       <c r="AD78">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="AE78">
         <v>0</v>
       </c>
       <c r="AF78">
-        <v>0.14</v>
+        <v>0.129</v>
       </c>
       <c r="AG78">
-        <v>0.23</v>
+        <v>0.201</v>
       </c>
       <c r="AH78">
         <v>0</v>
       </c>
       <c r="AI78">
-        <v>0.01999999999999999</v>
+        <v>0.01399999999999998</v>
       </c>
       <c r="AJ78">
-        <v>0.16</v>
+        <v>0.143</v>
       </c>
       <c r="AK78">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="AL78">
-        <v>15</v>
+        <v>12.3</v>
       </c>
       <c r="AM78">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AN78">
-        <v>45.2</v>
+        <v>47.8</v>
       </c>
       <c r="AO78">
-        <v>41.9</v>
+        <v>39.1</v>
       </c>
       <c r="AP78">
         <v>0</v>
       </c>
       <c r="AQ78">
-        <v>15.6</v>
+        <v>23.4</v>
       </c>
       <c r="AR78">
         <v>0</v>
@@ -13195,46 +13195,46 @@
         <v>197</v>
       </c>
       <c r="AD79">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF79">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="AG79">
-        <v>0.318</v>
+        <v>0.392</v>
       </c>
       <c r="AH79">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI79">
-        <v>0.09999999999999998</v>
+        <v>0.167</v>
       </c>
       <c r="AJ79">
-        <v>0.367</v>
+        <v>0.5</v>
       </c>
       <c r="AK79">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="AL79">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="AM79">
-        <v>2.99</v>
+        <v>4.27</v>
       </c>
       <c r="AN79">
-        <v>44</v>
+        <v>43.3</v>
       </c>
       <c r="AO79">
-        <v>28</v>
+        <v>26.7</v>
       </c>
       <c r="AP79">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ79">
-        <v>32</v>
+        <v>33.3</v>
       </c>
       <c r="AR79">
         <v>1</v>
@@ -13350,46 +13350,46 @@
         <v>198</v>
       </c>
       <c r="AD80">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="AE80">
         <v>0</v>
       </c>
       <c r="AF80">
-        <v>0.14</v>
+        <v>0.129</v>
       </c>
       <c r="AG80">
-        <v>0.23</v>
+        <v>0.201</v>
       </c>
       <c r="AH80">
         <v>0</v>
       </c>
       <c r="AI80">
-        <v>0.01999999999999999</v>
+        <v>0.01399999999999998</v>
       </c>
       <c r="AJ80">
-        <v>0.16</v>
+        <v>0.143</v>
       </c>
       <c r="AK80">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="AL80">
-        <v>15</v>
+        <v>12.3</v>
       </c>
       <c r="AM80">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AN80">
-        <v>45.2</v>
+        <v>47.8</v>
       </c>
       <c r="AO80">
-        <v>41.9</v>
+        <v>39.1</v>
       </c>
       <c r="AP80">
         <v>0</v>
       </c>
       <c r="AQ80">
-        <v>15.6</v>
+        <v>23.4</v>
       </c>
       <c r="AR80">
         <v>1</v>
@@ -13505,46 +13505,46 @@
         <v>197</v>
       </c>
       <c r="AD81">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF81">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="AG81">
-        <v>0.318</v>
+        <v>0.392</v>
       </c>
       <c r="AH81">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI81">
-        <v>0.09999999999999998</v>
+        <v>0.167</v>
       </c>
       <c r="AJ81">
-        <v>0.367</v>
+        <v>0.5</v>
       </c>
       <c r="AK81">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="AL81">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="AM81">
-        <v>2.99</v>
+        <v>4.27</v>
       </c>
       <c r="AN81">
-        <v>44</v>
+        <v>43.3</v>
       </c>
       <c r="AO81">
-        <v>28</v>
+        <v>26.7</v>
       </c>
       <c r="AP81">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ81">
-        <v>32</v>
+        <v>33.3</v>
       </c>
       <c r="AR81">
         <v>1</v>
@@ -13660,46 +13660,46 @@
         <v>198</v>
       </c>
       <c r="AD82">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="AE82">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF82">
-        <v>0.198</v>
+        <v>0.21</v>
       </c>
       <c r="AG82">
-        <v>0.2556631578947368</v>
+        <v>0.2677241379310345</v>
       </c>
       <c r="AH82">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI82">
-        <v>0.1342842105263158</v>
+        <v>0.1425070993914808</v>
       </c>
       <c r="AJ82">
-        <v>0.3323684210526315</v>
+        <v>0.3529716024340771</v>
       </c>
       <c r="AK82">
-        <v>22.324</v>
+        <v>22.301</v>
       </c>
       <c r="AL82">
-        <v>6.323157894736842</v>
+        <v>6.10081135902637</v>
       </c>
       <c r="AM82">
-        <v>3.328842105263158</v>
+        <v>3.357849898580121</v>
       </c>
       <c r="AN82">
-        <v>38.54421052631579</v>
+        <v>38.15070993914807</v>
       </c>
       <c r="AO82">
-        <v>41.5578947368421</v>
+        <v>41.326369168357</v>
       </c>
       <c r="AP82">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ82">
-        <v>32.03263157894737</v>
+        <v>31.62555780933063</v>
       </c>
       <c r="AR82">
         <v>1</v>
@@ -13815,46 +13815,46 @@
         <v>198</v>
       </c>
       <c r="AD83">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="AE83">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF83">
-        <v>0.198</v>
+        <v>0.21</v>
       </c>
       <c r="AG83">
-        <v>0.2556631578947368</v>
+        <v>0.2677241379310345</v>
       </c>
       <c r="AH83">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI83">
-        <v>0.1342842105263158</v>
+        <v>0.1425070993914808</v>
       </c>
       <c r="AJ83">
-        <v>0.3323684210526315</v>
+        <v>0.3529716024340771</v>
       </c>
       <c r="AK83">
-        <v>22.324</v>
+        <v>22.301</v>
       </c>
       <c r="AL83">
-        <v>6.323157894736842</v>
+        <v>6.10081135902637</v>
       </c>
       <c r="AM83">
-        <v>3.328842105263158</v>
+        <v>3.357849898580121</v>
       </c>
       <c r="AN83">
-        <v>38.54421052631579</v>
+        <v>38.15070993914807</v>
       </c>
       <c r="AO83">
-        <v>41.5578947368421</v>
+        <v>41.326369168357</v>
       </c>
       <c r="AP83">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ83">
-        <v>32.03263157894737</v>
+        <v>31.62555780933063</v>
       </c>
       <c r="AR83">
         <v>0</v>
@@ -13970,46 +13970,46 @@
         <v>198</v>
       </c>
       <c r="AD84">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="AE84">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF84">
-        <v>0.198</v>
+        <v>0.21</v>
       </c>
       <c r="AG84">
-        <v>0.2556631578947368</v>
+        <v>0.2677241379310345</v>
       </c>
       <c r="AH84">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI84">
-        <v>0.1342842105263158</v>
+        <v>0.1425070993914808</v>
       </c>
       <c r="AJ84">
-        <v>0.3323684210526315</v>
+        <v>0.3529716024340771</v>
       </c>
       <c r="AK84">
-        <v>22.324</v>
+        <v>22.301</v>
       </c>
       <c r="AL84">
-        <v>6.323157894736842</v>
+        <v>6.10081135902637</v>
       </c>
       <c r="AM84">
-        <v>3.328842105263158</v>
+        <v>3.357849898580121</v>
       </c>
       <c r="AN84">
-        <v>38.54421052631579</v>
+        <v>38.15070993914807</v>
       </c>
       <c r="AO84">
-        <v>41.5578947368421</v>
+        <v>41.326369168357</v>
       </c>
       <c r="AP84">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ84">
-        <v>32.03263157894737</v>
+        <v>31.62555780933063</v>
       </c>
       <c r="AR84">
         <v>1</v>
@@ -14125,46 +14125,46 @@
         <v>198</v>
       </c>
       <c r="AD85">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="AE85">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF85">
-        <v>0.198</v>
+        <v>0.21</v>
       </c>
       <c r="AG85">
-        <v>0.2556631578947368</v>
+        <v>0.2677241379310345</v>
       </c>
       <c r="AH85">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI85">
-        <v>0.1342842105263158</v>
+        <v>0.1425070993914808</v>
       </c>
       <c r="AJ85">
-        <v>0.3323684210526315</v>
+        <v>0.3529716024340771</v>
       </c>
       <c r="AK85">
-        <v>22.324</v>
+        <v>22.301</v>
       </c>
       <c r="AL85">
-        <v>6.323157894736842</v>
+        <v>6.10081135902637</v>
       </c>
       <c r="AM85">
-        <v>3.328842105263158</v>
+        <v>3.357849898580121</v>
       </c>
       <c r="AN85">
-        <v>38.54421052631579</v>
+        <v>38.15070993914807</v>
       </c>
       <c r="AO85">
-        <v>41.5578947368421</v>
+        <v>41.326369168357</v>
       </c>
       <c r="AP85">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ85">
-        <v>32.03263157894737</v>
+        <v>31.62555780933063</v>
       </c>
       <c r="AR85">
         <v>1</v>
@@ -14280,46 +14280,46 @@
         <v>197</v>
       </c>
       <c r="AD86">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AE86">
         <v>15</v>
       </c>
       <c r="AF86">
-        <v>0.233</v>
+        <v>0.232</v>
       </c>
       <c r="AG86">
-        <v>0.2860309278350515</v>
+        <v>0.2842708757637474</v>
       </c>
       <c r="AH86">
         <v>3.1</v>
       </c>
       <c r="AI86">
-        <v>0.1414432989690722</v>
+        <v>0.1395030549898167</v>
       </c>
       <c r="AJ86">
-        <v>0.3744948453608248</v>
+        <v>0.3717230142566191</v>
       </c>
       <c r="AK86">
-        <v>25.966</v>
+        <v>25.847</v>
       </c>
       <c r="AL86">
-        <v>5.971134020618557</v>
+        <v>5.892057026476579</v>
       </c>
       <c r="AM86">
-        <v>3.432061855670103</v>
+        <v>3.411588594704685</v>
       </c>
       <c r="AN86">
-        <v>35.92268041237114</v>
+        <v>36.24867617107943</v>
       </c>
       <c r="AO86">
-        <v>42.14845360824742</v>
+        <v>41.82484725050917</v>
       </c>
       <c r="AP86">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="AQ86">
-        <v>39.45773195876289</v>
+        <v>39.48187372708758</v>
       </c>
       <c r="AR86">
         <v>1</v>
@@ -14435,46 +14435,46 @@
         <v>197</v>
       </c>
       <c r="AD87">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AE87">
         <v>15</v>
       </c>
       <c r="AF87">
-        <v>0.233</v>
+        <v>0.232</v>
       </c>
       <c r="AG87">
-        <v>0.2860309278350515</v>
+        <v>0.2842708757637474</v>
       </c>
       <c r="AH87">
         <v>3.1</v>
       </c>
       <c r="AI87">
-        <v>0.1414432989690722</v>
+        <v>0.1395030549898167</v>
       </c>
       <c r="AJ87">
-        <v>0.3744948453608248</v>
+        <v>0.3717230142566191</v>
       </c>
       <c r="AK87">
-        <v>25.966</v>
+        <v>25.847</v>
       </c>
       <c r="AL87">
-        <v>5.971134020618557</v>
+        <v>5.892057026476579</v>
       </c>
       <c r="AM87">
-        <v>3.432061855670103</v>
+        <v>3.411588594704685</v>
       </c>
       <c r="AN87">
-        <v>35.92268041237114</v>
+        <v>36.24867617107943</v>
       </c>
       <c r="AO87">
-        <v>42.14845360824742</v>
+        <v>41.82484725050917</v>
       </c>
       <c r="AP87">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="AQ87">
-        <v>39.45773195876289</v>
+        <v>39.48187372708758</v>
       </c>
       <c r="AR87">
         <v>0</v>
@@ -14590,46 +14590,46 @@
         <v>198</v>
       </c>
       <c r="AD88">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="AE88">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF88">
-        <v>0.198</v>
+        <v>0.21</v>
       </c>
       <c r="AG88">
-        <v>0.2556631578947368</v>
+        <v>0.2677241379310345</v>
       </c>
       <c r="AH88">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI88">
-        <v>0.1342842105263158</v>
+        <v>0.1425070993914808</v>
       </c>
       <c r="AJ88">
-        <v>0.3323684210526315</v>
+        <v>0.3529716024340771</v>
       </c>
       <c r="AK88">
-        <v>22.324</v>
+        <v>22.301</v>
       </c>
       <c r="AL88">
-        <v>6.323157894736842</v>
+        <v>6.10081135902637</v>
       </c>
       <c r="AM88">
-        <v>3.328842105263158</v>
+        <v>3.357849898580121</v>
       </c>
       <c r="AN88">
-        <v>38.54421052631579</v>
+        <v>38.15070993914807</v>
       </c>
       <c r="AO88">
-        <v>41.5578947368421</v>
+        <v>41.326369168357</v>
       </c>
       <c r="AP88">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ88">
-        <v>32.03263157894737</v>
+        <v>31.62555780933063</v>
       </c>
       <c r="AR88">
         <v>1</v>
@@ -14745,46 +14745,46 @@
         <v>198</v>
       </c>
       <c r="AD89">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="AE89">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF89">
-        <v>0.198</v>
+        <v>0.21</v>
       </c>
       <c r="AG89">
-        <v>0.2556631578947368</v>
+        <v>0.2677241379310345</v>
       </c>
       <c r="AH89">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI89">
-        <v>0.1342842105263158</v>
+        <v>0.1425070993914808</v>
       </c>
       <c r="AJ89">
-        <v>0.3323684210526315</v>
+        <v>0.3529716024340771</v>
       </c>
       <c r="AK89">
-        <v>22.324</v>
+        <v>22.301</v>
       </c>
       <c r="AL89">
-        <v>6.323157894736842</v>
+        <v>6.10081135902637</v>
       </c>
       <c r="AM89">
-        <v>3.328842105263158</v>
+        <v>3.357849898580121</v>
       </c>
       <c r="AN89">
-        <v>38.54421052631579</v>
+        <v>38.15070993914807</v>
       </c>
       <c r="AO89">
-        <v>41.5578947368421</v>
+        <v>41.326369168357</v>
       </c>
       <c r="AP89">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ89">
-        <v>32.03263157894737</v>
+        <v>31.62555780933063</v>
       </c>
       <c r="AR89">
         <v>1</v>
@@ -14900,46 +14900,46 @@
         <v>197</v>
       </c>
       <c r="AD90">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AE90">
         <v>15</v>
       </c>
       <c r="AF90">
-        <v>0.233</v>
+        <v>0.232</v>
       </c>
       <c r="AG90">
-        <v>0.2860309278350515</v>
+        <v>0.2842708757637474</v>
       </c>
       <c r="AH90">
         <v>3.1</v>
       </c>
       <c r="AI90">
-        <v>0.1414432989690722</v>
+        <v>0.1395030549898167</v>
       </c>
       <c r="AJ90">
-        <v>0.3744948453608248</v>
+        <v>0.3717230142566191</v>
       </c>
       <c r="AK90">
-        <v>25.966</v>
+        <v>25.847</v>
       </c>
       <c r="AL90">
-        <v>5.971134020618557</v>
+        <v>5.892057026476579</v>
       </c>
       <c r="AM90">
-        <v>3.432061855670103</v>
+        <v>3.411588594704685</v>
       </c>
       <c r="AN90">
-        <v>35.92268041237114</v>
+        <v>36.24867617107943</v>
       </c>
       <c r="AO90">
-        <v>42.14845360824742</v>
+        <v>41.82484725050917</v>
       </c>
       <c r="AP90">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="AQ90">
-        <v>39.45773195876289</v>
+        <v>39.48187372708758</v>
       </c>
       <c r="AR90">
         <v>0</v>
@@ -15055,46 +15055,46 @@
         <v>198</v>
       </c>
       <c r="AD91">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="AE91">
         <v>10</v>
       </c>
       <c r="AF91">
-        <v>0.261</v>
+        <v>0.254</v>
       </c>
       <c r="AG91">
-        <v>0.3445798045602606</v>
+        <v>0.3366206896551724</v>
       </c>
       <c r="AH91">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AI91">
-        <v>0.1801824104234528</v>
+        <v>0.1734420062695925</v>
       </c>
       <c r="AJ91">
-        <v>0.4408925081433225</v>
+        <v>0.4275423197492163</v>
       </c>
       <c r="AK91">
-        <v>24.412</v>
+        <v>23.813</v>
       </c>
       <c r="AL91">
-        <v>8.124755700325732</v>
+        <v>8.127586206896552</v>
       </c>
       <c r="AM91">
-        <v>4.297328990228013</v>
+        <v>4.258683385579937</v>
       </c>
       <c r="AN91">
-        <v>43.13648208469056</v>
+        <v>44.39529780564263</v>
       </c>
       <c r="AO91">
-        <v>36.52312703583062</v>
+        <v>35.33730407523511</v>
       </c>
       <c r="AP91">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="AQ91">
-        <v>36.72801302931596</v>
+        <v>36.3319749216301</v>
       </c>
       <c r="AR91">
         <v>0</v>
@@ -15210,46 +15210,46 @@
         <v>198</v>
       </c>
       <c r="AD92">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="AE92">
         <v>10</v>
       </c>
       <c r="AF92">
-        <v>0.261</v>
+        <v>0.254</v>
       </c>
       <c r="AG92">
-        <v>0.3445798045602606</v>
+        <v>0.3366206896551724</v>
       </c>
       <c r="AH92">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AI92">
-        <v>0.1801824104234528</v>
+        <v>0.1734420062695925</v>
       </c>
       <c r="AJ92">
-        <v>0.4408925081433225</v>
+        <v>0.4275423197492163</v>
       </c>
       <c r="AK92">
-        <v>24.412</v>
+        <v>23.813</v>
       </c>
       <c r="AL92">
-        <v>8.124755700325732</v>
+        <v>8.127586206896552</v>
       </c>
       <c r="AM92">
-        <v>4.297328990228013</v>
+        <v>4.258683385579937</v>
       </c>
       <c r="AN92">
-        <v>43.13648208469056</v>
+        <v>44.39529780564263</v>
       </c>
       <c r="AO92">
-        <v>36.52312703583062</v>
+        <v>35.33730407523511</v>
       </c>
       <c r="AP92">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="AQ92">
-        <v>36.72801302931596</v>
+        <v>36.3319749216301</v>
       </c>
       <c r="AR92">
         <v>0</v>
@@ -15365,46 +15365,46 @@
         <v>198</v>
       </c>
       <c r="AD93">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="AE93">
         <v>10</v>
       </c>
       <c r="AF93">
-        <v>0.261</v>
+        <v>0.254</v>
       </c>
       <c r="AG93">
-        <v>0.3445798045602606</v>
+        <v>0.3366206896551724</v>
       </c>
       <c r="AH93">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AI93">
-        <v>0.1801824104234528</v>
+        <v>0.1734420062695925</v>
       </c>
       <c r="AJ93">
-        <v>0.4408925081433225</v>
+        <v>0.4275423197492163</v>
       </c>
       <c r="AK93">
-        <v>24.412</v>
+        <v>23.813</v>
       </c>
       <c r="AL93">
-        <v>8.124755700325732</v>
+        <v>8.127586206896552</v>
       </c>
       <c r="AM93">
-        <v>4.297328990228013</v>
+        <v>4.258683385579937</v>
       </c>
       <c r="AN93">
-        <v>43.13648208469056</v>
+        <v>44.39529780564263</v>
       </c>
       <c r="AO93">
-        <v>36.52312703583062</v>
+        <v>35.33730407523511</v>
       </c>
       <c r="AP93">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="AQ93">
-        <v>36.72801302931596</v>
+        <v>36.3319749216301</v>
       </c>
       <c r="AR93">
         <v>0</v>
@@ -15520,7 +15520,7 @@
         <v>197</v>
       </c>
       <c r="AD94">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="AE94">
         <v>6</v>
@@ -15529,37 +15529,37 @@
         <v>0.205</v>
       </c>
       <c r="AG94">
-        <v>0.2794340425531915</v>
+        <v>0.2754</v>
       </c>
       <c r="AH94">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AI94">
-        <v>0.1278425531914893</v>
+        <v>0.1222571428571429</v>
       </c>
       <c r="AJ94">
-        <v>0.3328382978723404</v>
+        <v>0.3268285714285715</v>
       </c>
       <c r="AK94">
-        <v>26.397</v>
+        <v>26.949</v>
       </c>
       <c r="AL94">
-        <v>6.357446808510638</v>
+        <v>6.091428571428572</v>
       </c>
       <c r="AM94">
-        <v>3.586212765957447</v>
+        <v>3.442857142857143</v>
       </c>
       <c r="AN94">
-        <v>41.20468085106383</v>
+        <v>41.54571428571428</v>
       </c>
       <c r="AO94">
-        <v>45.27148936170212</v>
+        <v>44.16857142857143</v>
       </c>
       <c r="AP94">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ94">
-        <v>30.90255319148936</v>
+        <v>31</v>
       </c>
       <c r="AR94">
         <v>1</v>
@@ -15675,46 +15675,46 @@
         <v>198</v>
       </c>
       <c r="AD95">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="AE95">
         <v>10</v>
       </c>
       <c r="AF95">
-        <v>0.261</v>
+        <v>0.254</v>
       </c>
       <c r="AG95">
-        <v>0.3445798045602606</v>
+        <v>0.3366206896551724</v>
       </c>
       <c r="AH95">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AI95">
-        <v>0.1801824104234528</v>
+        <v>0.1734420062695925</v>
       </c>
       <c r="AJ95">
-        <v>0.4408925081433225</v>
+        <v>0.4275423197492163</v>
       </c>
       <c r="AK95">
-        <v>24.412</v>
+        <v>23.813</v>
       </c>
       <c r="AL95">
-        <v>8.124755700325732</v>
+        <v>8.127586206896552</v>
       </c>
       <c r="AM95">
-        <v>4.297328990228013</v>
+        <v>4.258683385579937</v>
       </c>
       <c r="AN95">
-        <v>43.13648208469056</v>
+        <v>44.39529780564263</v>
       </c>
       <c r="AO95">
-        <v>36.52312703583062</v>
+        <v>35.33730407523511</v>
       </c>
       <c r="AP95">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="AQ95">
-        <v>36.72801302931596</v>
+        <v>36.3319749216301</v>
       </c>
       <c r="AR95">
         <v>0</v>
@@ -15830,7 +15830,7 @@
         <v>197</v>
       </c>
       <c r="AD96">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="AE96">
         <v>6</v>
@@ -15839,37 +15839,37 @@
         <v>0.205</v>
       </c>
       <c r="AG96">
-        <v>0.2794340425531915</v>
+        <v>0.2754</v>
       </c>
       <c r="AH96">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AI96">
-        <v>0.1278425531914893</v>
+        <v>0.1222571428571429</v>
       </c>
       <c r="AJ96">
-        <v>0.3328382978723404</v>
+        <v>0.3268285714285715</v>
       </c>
       <c r="AK96">
-        <v>26.397</v>
+        <v>26.949</v>
       </c>
       <c r="AL96">
-        <v>6.357446808510638</v>
+        <v>6.091428571428572</v>
       </c>
       <c r="AM96">
-        <v>3.586212765957447</v>
+        <v>3.442857142857143</v>
       </c>
       <c r="AN96">
-        <v>41.20468085106383</v>
+        <v>41.54571428571428</v>
       </c>
       <c r="AO96">
-        <v>45.27148936170212</v>
+        <v>44.16857142857143</v>
       </c>
       <c r="AP96">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ96">
-        <v>30.90255319148936</v>
+        <v>31</v>
       </c>
       <c r="AR96">
         <v>1</v>
@@ -15985,7 +15985,7 @@
         <v>197</v>
       </c>
       <c r="AD97">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="AE97">
         <v>6</v>
@@ -15994,37 +15994,37 @@
         <v>0.205</v>
       </c>
       <c r="AG97">
-        <v>0.2794340425531915</v>
+        <v>0.2754</v>
       </c>
       <c r="AH97">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AI97">
-        <v>0.1278425531914893</v>
+        <v>0.1222571428571429</v>
       </c>
       <c r="AJ97">
-        <v>0.3328382978723404</v>
+        <v>0.3268285714285715</v>
       </c>
       <c r="AK97">
-        <v>26.397</v>
+        <v>26.949</v>
       </c>
       <c r="AL97">
-        <v>6.357446808510638</v>
+        <v>6.091428571428572</v>
       </c>
       <c r="AM97">
-        <v>3.586212765957447</v>
+        <v>3.442857142857143</v>
       </c>
       <c r="AN97">
-        <v>41.20468085106383</v>
+        <v>41.54571428571428</v>
       </c>
       <c r="AO97">
-        <v>45.27148936170212</v>
+        <v>44.16857142857143</v>
       </c>
       <c r="AP97">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ97">
-        <v>30.90255319148936</v>
+        <v>31</v>
       </c>
       <c r="AR97">
         <v>1</v>
@@ -16140,46 +16140,46 @@
         <v>198</v>
       </c>
       <c r="AD98">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="AE98">
         <v>10</v>
       </c>
       <c r="AF98">
-        <v>0.261</v>
+        <v>0.254</v>
       </c>
       <c r="AG98">
-        <v>0.3445798045602606</v>
+        <v>0.3366206896551724</v>
       </c>
       <c r="AH98">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AI98">
-        <v>0.1801824104234528</v>
+        <v>0.1734420062695925</v>
       </c>
       <c r="AJ98">
-        <v>0.4408925081433225</v>
+        <v>0.4275423197492163</v>
       </c>
       <c r="AK98">
-        <v>24.412</v>
+        <v>23.813</v>
       </c>
       <c r="AL98">
-        <v>8.124755700325732</v>
+        <v>8.127586206896552</v>
       </c>
       <c r="AM98">
-        <v>4.297328990228013</v>
+        <v>4.258683385579937</v>
       </c>
       <c r="AN98">
-        <v>43.13648208469056</v>
+        <v>44.39529780564263</v>
       </c>
       <c r="AO98">
-        <v>36.52312703583062</v>
+        <v>35.33730407523511</v>
       </c>
       <c r="AP98">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="AQ98">
-        <v>36.72801302931596</v>
+        <v>36.3319749216301</v>
       </c>
       <c r="AR98">
         <v>1</v>
@@ -16295,7 +16295,7 @@
         <v>197</v>
       </c>
       <c r="AD99">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="AE99">
         <v>6</v>
@@ -16304,37 +16304,37 @@
         <v>0.205</v>
       </c>
       <c r="AG99">
-        <v>0.2794340425531915</v>
+        <v>0.2754</v>
       </c>
       <c r="AH99">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AI99">
-        <v>0.1278425531914893</v>
+        <v>0.1222571428571429</v>
       </c>
       <c r="AJ99">
-        <v>0.3328382978723404</v>
+        <v>0.3268285714285715</v>
       </c>
       <c r="AK99">
-        <v>26.397</v>
+        <v>26.949</v>
       </c>
       <c r="AL99">
-        <v>6.357446808510638</v>
+        <v>6.091428571428572</v>
       </c>
       <c r="AM99">
-        <v>3.586212765957447</v>
+        <v>3.442857142857143</v>
       </c>
       <c r="AN99">
-        <v>41.20468085106383</v>
+        <v>41.54571428571428</v>
       </c>
       <c r="AO99">
-        <v>45.27148936170212</v>
+        <v>44.16857142857143</v>
       </c>
       <c r="AP99">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ99">
-        <v>30.90255319148936</v>
+        <v>31</v>
       </c>
       <c r="AR99">
         <v>1</v>
@@ -16450,46 +16450,46 @@
         <v>198</v>
       </c>
       <c r="AD100">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="AE100">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF100">
-        <v>0.23</v>
+        <v>0.231</v>
       </c>
       <c r="AG100">
-        <v>0.2906587677725119</v>
+        <v>0.2931290322580645</v>
       </c>
       <c r="AH100">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AI100">
-        <v>0.1446587677725119</v>
+        <v>0.1484193548387097</v>
       </c>
       <c r="AJ100">
-        <v>0.3747914691943128</v>
+        <v>0.3795161290322581</v>
       </c>
       <c r="AK100">
-        <v>24.864</v>
+        <v>24.406</v>
       </c>
       <c r="AL100">
-        <v>6.61042654028436</v>
+        <v>6.670967741935484</v>
       </c>
       <c r="AM100">
-        <v>3.901563981042655</v>
+        <v>4.022903225806452</v>
       </c>
       <c r="AN100">
-        <v>44.01137440758294</v>
+        <v>44.18064516129032</v>
       </c>
       <c r="AO100">
-        <v>37.89620853080569</v>
+        <v>38.00967741935484</v>
       </c>
       <c r="AP100">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="AQ100">
-        <v>33.33364928909953</v>
+        <v>32.56774193548387</v>
       </c>
       <c r="AR100">
         <v>0</v>
@@ -16605,46 +16605,46 @@
         <v>198</v>
       </c>
       <c r="AD101">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="AE101">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF101">
-        <v>0.23</v>
+        <v>0.231</v>
       </c>
       <c r="AG101">
-        <v>0.2906587677725119</v>
+        <v>0.2931290322580645</v>
       </c>
       <c r="AH101">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AI101">
-        <v>0.1446587677725119</v>
+        <v>0.1484193548387097</v>
       </c>
       <c r="AJ101">
-        <v>0.3747914691943128</v>
+        <v>0.3795161290322581</v>
       </c>
       <c r="AK101">
-        <v>24.864</v>
+        <v>24.406</v>
       </c>
       <c r="AL101">
-        <v>6.61042654028436</v>
+        <v>6.670967741935484</v>
       </c>
       <c r="AM101">
-        <v>3.901563981042655</v>
+        <v>4.022903225806452</v>
       </c>
       <c r="AN101">
-        <v>44.01137440758294</v>
+        <v>44.18064516129032</v>
       </c>
       <c r="AO101">
-        <v>37.89620853080569</v>
+        <v>38.00967741935484</v>
       </c>
       <c r="AP101">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="AQ101">
-        <v>33.33364928909953</v>
+        <v>32.56774193548387</v>
       </c>
       <c r="AR101">
         <v>1</v>
@@ -16760,46 +16760,46 @@
         <v>198</v>
       </c>
       <c r="AD102">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="AE102">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF102">
-        <v>0.23</v>
+        <v>0.231</v>
       </c>
       <c r="AG102">
-        <v>0.2906587677725119</v>
+        <v>0.2931290322580645</v>
       </c>
       <c r="AH102">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AI102">
-        <v>0.1446587677725119</v>
+        <v>0.1484193548387097</v>
       </c>
       <c r="AJ102">
-        <v>0.3747914691943128</v>
+        <v>0.3795161290322581</v>
       </c>
       <c r="AK102">
-        <v>24.864</v>
+        <v>24.406</v>
       </c>
       <c r="AL102">
-        <v>6.61042654028436</v>
+        <v>6.670967741935484</v>
       </c>
       <c r="AM102">
-        <v>3.901563981042655</v>
+        <v>4.022903225806452</v>
       </c>
       <c r="AN102">
-        <v>44.01137440758294</v>
+        <v>44.18064516129032</v>
       </c>
       <c r="AO102">
-        <v>37.89620853080569</v>
+        <v>38.00967741935484</v>
       </c>
       <c r="AP102">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="AQ102">
-        <v>33.33364928909953</v>
+        <v>32.56774193548387</v>
       </c>
       <c r="AR102">
         <v>1</v>
@@ -16915,46 +16915,46 @@
         <v>197</v>
       </c>
       <c r="AD103">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="AE103">
         <v>9</v>
       </c>
       <c r="AF103">
-        <v>0.187</v>
+        <v>0.184</v>
       </c>
       <c r="AG103">
-        <v>0.2333870967741935</v>
+        <v>0.2280996884735202</v>
       </c>
       <c r="AH103">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AI103">
-        <v>0.1125193548387097</v>
+        <v>0.1085295950155763</v>
       </c>
       <c r="AJ103">
-        <v>0.2999064516129032</v>
+        <v>0.2926168224299065</v>
       </c>
       <c r="AK103">
-        <v>19.009</v>
+        <v>19.919</v>
       </c>
       <c r="AL103">
-        <v>4.835806451612903</v>
+        <v>4.670093457943925</v>
       </c>
       <c r="AM103">
-        <v>3.702709677419355</v>
+        <v>3.576417445482866</v>
       </c>
       <c r="AN103">
-        <v>55.85387096774193</v>
+        <v>55.21962616822429</v>
       </c>
       <c r="AO103">
-        <v>29.80774193548387</v>
+        <v>30.45233644859813</v>
       </c>
       <c r="AP103">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="AQ103">
-        <v>31.46677419354839</v>
+        <v>31.101246105919</v>
       </c>
       <c r="AR103">
         <v>1</v>
@@ -17070,46 +17070,46 @@
         <v>197</v>
       </c>
       <c r="AD104">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="AE104">
         <v>9</v>
       </c>
       <c r="AF104">
-        <v>0.187</v>
+        <v>0.184</v>
       </c>
       <c r="AG104">
-        <v>0.2333870967741935</v>
+        <v>0.2280996884735202</v>
       </c>
       <c r="AH104">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AI104">
-        <v>0.1125193548387097</v>
+        <v>0.1085295950155763</v>
       </c>
       <c r="AJ104">
-        <v>0.2999064516129032</v>
+        <v>0.2926168224299065</v>
       </c>
       <c r="AK104">
-        <v>19.009</v>
+        <v>19.919</v>
       </c>
       <c r="AL104">
-        <v>4.835806451612903</v>
+        <v>4.670093457943925</v>
       </c>
       <c r="AM104">
-        <v>3.702709677419355</v>
+        <v>3.576417445482866</v>
       </c>
       <c r="AN104">
-        <v>55.85387096774193</v>
+        <v>55.21962616822429</v>
       </c>
       <c r="AO104">
-        <v>29.80774193548387</v>
+        <v>30.45233644859813</v>
       </c>
       <c r="AP104">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="AQ104">
-        <v>31.46677419354839</v>
+        <v>31.101246105919</v>
       </c>
       <c r="AR104">
         <v>0</v>
@@ -17225,46 +17225,46 @@
         <v>197</v>
       </c>
       <c r="AD105">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="AE105">
         <v>9</v>
       </c>
       <c r="AF105">
-        <v>0.187</v>
+        <v>0.184</v>
       </c>
       <c r="AG105">
-        <v>0.2333870967741935</v>
+        <v>0.2280996884735202</v>
       </c>
       <c r="AH105">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AI105">
-        <v>0.1125193548387097</v>
+        <v>0.1085295950155763</v>
       </c>
       <c r="AJ105">
-        <v>0.2999064516129032</v>
+        <v>0.2926168224299065</v>
       </c>
       <c r="AK105">
-        <v>19.009</v>
+        <v>19.919</v>
       </c>
       <c r="AL105">
-        <v>4.835806451612903</v>
+        <v>4.670093457943925</v>
       </c>
       <c r="AM105">
-        <v>3.702709677419355</v>
+        <v>3.576417445482866</v>
       </c>
       <c r="AN105">
-        <v>55.85387096774193</v>
+        <v>55.21962616822429</v>
       </c>
       <c r="AO105">
-        <v>29.80774193548387</v>
+        <v>30.45233644859813</v>
       </c>
       <c r="AP105">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="AQ105">
-        <v>31.46677419354839</v>
+        <v>31.101246105919</v>
       </c>
       <c r="AR105">
         <v>0</v>
@@ -17380,46 +17380,46 @@
         <v>198</v>
       </c>
       <c r="AD106">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="AE106">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF106">
-        <v>0.23</v>
+        <v>0.231</v>
       </c>
       <c r="AG106">
-        <v>0.2906587677725119</v>
+        <v>0.2931290322580645</v>
       </c>
       <c r="AH106">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AI106">
-        <v>0.1446587677725119</v>
+        <v>0.1484193548387097</v>
       </c>
       <c r="AJ106">
-        <v>0.3747914691943128</v>
+        <v>0.3795161290322581</v>
       </c>
       <c r="AK106">
-        <v>24.864</v>
+        <v>24.406</v>
       </c>
       <c r="AL106">
-        <v>6.61042654028436</v>
+        <v>6.670967741935484</v>
       </c>
       <c r="AM106">
-        <v>3.901563981042655</v>
+        <v>4.022903225806452</v>
       </c>
       <c r="AN106">
-        <v>44.01137440758294</v>
+        <v>44.18064516129032</v>
       </c>
       <c r="AO106">
-        <v>37.89620853080569</v>
+        <v>38.00967741935484</v>
       </c>
       <c r="AP106">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="AQ106">
-        <v>33.33364928909953</v>
+        <v>32.56774193548387</v>
       </c>
       <c r="AR106">
         <v>1</v>
@@ -17535,46 +17535,46 @@
         <v>197</v>
       </c>
       <c r="AD107">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="AE107">
         <v>9</v>
       </c>
       <c r="AF107">
-        <v>0.187</v>
+        <v>0.184</v>
       </c>
       <c r="AG107">
-        <v>0.2333870967741935</v>
+        <v>0.2280996884735202</v>
       </c>
       <c r="AH107">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AI107">
-        <v>0.1125193548387097</v>
+        <v>0.1085295950155763</v>
       </c>
       <c r="AJ107">
-        <v>0.2999064516129032</v>
+        <v>0.2926168224299065</v>
       </c>
       <c r="AK107">
-        <v>19.009</v>
+        <v>19.919</v>
       </c>
       <c r="AL107">
-        <v>4.835806451612903</v>
+        <v>4.670093457943925</v>
       </c>
       <c r="AM107">
-        <v>3.702709677419355</v>
+        <v>3.576417445482866</v>
       </c>
       <c r="AN107">
-        <v>55.85387096774193</v>
+        <v>55.21962616822429</v>
       </c>
       <c r="AO107">
-        <v>29.80774193548387</v>
+        <v>30.45233644859813</v>
       </c>
       <c r="AP107">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="AQ107">
-        <v>31.46677419354839</v>
+        <v>31.101246105919</v>
       </c>
       <c r="AR107">
         <v>1</v>
@@ -17690,46 +17690,46 @@
         <v>197</v>
       </c>
       <c r="AD108">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="AE108">
         <v>9</v>
       </c>
       <c r="AF108">
-        <v>0.187</v>
+        <v>0.184</v>
       </c>
       <c r="AG108">
-        <v>0.2333870967741935</v>
+        <v>0.2280996884735202</v>
       </c>
       <c r="AH108">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AI108">
-        <v>0.1125193548387097</v>
+        <v>0.1085295950155763</v>
       </c>
       <c r="AJ108">
-        <v>0.2999064516129032</v>
+        <v>0.2926168224299065</v>
       </c>
       <c r="AK108">
-        <v>19.009</v>
+        <v>19.919</v>
       </c>
       <c r="AL108">
-        <v>4.835806451612903</v>
+        <v>4.670093457943925</v>
       </c>
       <c r="AM108">
-        <v>3.702709677419355</v>
+        <v>3.576417445482866</v>
       </c>
       <c r="AN108">
-        <v>55.85387096774193</v>
+        <v>55.21962616822429</v>
       </c>
       <c r="AO108">
-        <v>29.80774193548387</v>
+        <v>30.45233644859813</v>
       </c>
       <c r="AP108">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="AQ108">
-        <v>31.46677419354839</v>
+        <v>31.101246105919</v>
       </c>
       <c r="AR108">
         <v>0</v>
